--- a/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Order_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Order_by_Sample_Type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
   <si>
     <t xml:space="preserve">Sample_Type</t>
   </si>
@@ -456,30 +456,30 @@
     <t xml:space="preserve">RBG-16-55-12_Unclassified</t>
   </si>
   <si>
+    <t xml:space="preserve">Methanobacteriota_Unclassified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isosphaerales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steroidobacterales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD2896-B216_Unclassified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldarchaeales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polyangiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAR202_clade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rickettsiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Methanobacteriota_Unclassified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isosphaerales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steroidobacterales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MD2896-B216_Unclassified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caldarchaeales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polyangiales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAR202_clade</t>
-  </si>
-  <si>
     <t xml:space="preserve">Syntrophobacterales</t>
   </si>
   <si>
@@ -696,9 +696,6 @@
     <t xml:space="preserve">LD1-PB3</t>
   </si>
   <si>
-    <t xml:space="preserve">Chloroplast</t>
-  </si>
-  <si>
     <t xml:space="preserve">VHS-B4-70</t>
   </si>
   <si>
@@ -957,12 +954,12 @@
     <t xml:space="preserve">Dissulfuribacterales</t>
   </si>
   <si>
+    <t xml:space="preserve">Vampirovibrionales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Candidatus_Moranbacteria</t>
   </si>
   <si>
-    <t xml:space="preserve">Vampirovibrionales</t>
-  </si>
-  <si>
     <t xml:space="preserve">DG-56_Unclassified</t>
   </si>
   <si>
@@ -975,13 +972,13 @@
     <t xml:space="preserve">Pedosphaerales</t>
   </si>
   <si>
+    <t xml:space="preserve">Caedibacterales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peptococcales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legionellales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caedibacterales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peptococcales</t>
   </si>
   <si>
     <t xml:space="preserve">Acidobacteriota_Unclassified</t>
@@ -1395,10 +1392,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>12.4639295819322</v>
+        <v>12.4651991687992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.448285918697067</v>
+        <v>0.448345278704398</v>
       </c>
     </row>
     <row r="3">
@@ -1409,10 +1406,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>5.78196952153187</v>
+        <v>5.78175384328398</v>
       </c>
       <c r="D3" t="n">
-        <v>0.173895046899155</v>
+        <v>0.173891851031029</v>
       </c>
     </row>
     <row r="4">
@@ -1423,10 +1420,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>5.16736703877692</v>
+        <v>5.16702265356048</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1540363024839</v>
+        <v>0.154022943881012</v>
       </c>
     </row>
     <row r="5">
@@ -1437,10 +1434,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>4.75112364897646</v>
+        <v>4.75077424714615</v>
       </c>
       <c r="D5" t="n">
-        <v>0.129801582746227</v>
+        <v>0.129793138447533</v>
       </c>
     </row>
     <row r="6">
@@ -1451,10 +1448,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2424128818126</v>
+        <v>4.24103928092586</v>
       </c>
       <c r="D6" t="n">
-        <v>0.780268806194848</v>
+        <v>0.779953745051578</v>
       </c>
     </row>
     <row r="7">
@@ -1465,10 +1462,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3.40976468453934</v>
+        <v>3.40983508152703</v>
       </c>
       <c r="D7" t="n">
-        <v>0.197089448395916</v>
+        <v>0.197090472795478</v>
       </c>
     </row>
     <row r="8">
@@ -1479,10 +1476,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.19076646684048</v>
+        <v>3.19065981940456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.109878038551015</v>
+        <v>0.109874070769023</v>
       </c>
     </row>
     <row r="9">
@@ -1493,10 +1490,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.15596309415241</v>
+        <v>3.15587678225824</v>
       </c>
       <c r="D9" t="n">
-        <v>0.174451677946733</v>
+        <v>0.174437328289574</v>
       </c>
     </row>
     <row r="10">
@@ -1507,10 +1504,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2.94775463378045</v>
+        <v>2.94806372159539</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0717211799235303</v>
+        <v>0.07173198581819</v>
       </c>
     </row>
     <row r="11">
@@ -1521,10 +1518,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>2.90127445670132</v>
+        <v>2.90133396600686</v>
       </c>
       <c r="D11" t="n">
-        <v>0.219199471486179</v>
+        <v>0.219211683367185</v>
       </c>
     </row>
     <row r="12">
@@ -1535,10 +1532,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>2.84902491751544</v>
+        <v>2.8493668849347</v>
       </c>
       <c r="D12" t="n">
-        <v>0.35783584651224</v>
+        <v>0.35788589441473</v>
       </c>
     </row>
     <row r="13">
@@ -1549,10 +1546,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>2.65420584469443</v>
+        <v>2.65417142646859</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0503166392474722</v>
+        <v>0.0503160334179358</v>
       </c>
     </row>
     <row r="14">
@@ -1563,10 +1560,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>2.38729825062195</v>
+        <v>2.38739613161961</v>
       </c>
       <c r="D14" t="n">
-        <v>0.319167766070598</v>
+        <v>0.319182762232658</v>
       </c>
     </row>
     <row r="15">
@@ -1577,10 +1574,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>2.35106962378731</v>
+        <v>2.35099639736867</v>
       </c>
       <c r="D15" t="n">
-        <v>0.086795855462782</v>
+        <v>0.0867918112182207</v>
       </c>
     </row>
     <row r="16">
@@ -1591,10 +1588,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>2.16120215614226</v>
+        <v>2.16190915247882</v>
       </c>
       <c r="D16" t="n">
-        <v>0.630839632185262</v>
+        <v>0.631046876611651</v>
       </c>
     </row>
     <row r="17">
@@ -1605,10 +1602,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.90893778431146</v>
+        <v>1.90882468499328</v>
       </c>
       <c r="D17" t="n">
-        <v>0.128621965407499</v>
+        <v>0.128611903533638</v>
       </c>
     </row>
     <row r="18">
@@ -1619,10 +1616,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.60443809805352</v>
+        <v>1.6045568246363</v>
       </c>
       <c r="D18" t="n">
-        <v>1.02470187994274</v>
+        <v>1.02480571441199</v>
       </c>
     </row>
     <row r="19">
@@ -1633,10 +1630,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.58070642185568</v>
+        <v>1.58092459863834</v>
       </c>
       <c r="D19" t="n">
-        <v>0.137735164731526</v>
+        <v>0.137756415495388</v>
       </c>
     </row>
     <row r="20">
@@ -1647,10 +1644,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>1.40420800480184</v>
+        <v>1.40425739542574</v>
       </c>
       <c r="D20" t="n">
-        <v>0.185993338485904</v>
+        <v>0.186003628800126</v>
       </c>
     </row>
     <row r="21">
@@ -1661,10 +1658,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>1.30185458681485</v>
+        <v>1.30212288353511</v>
       </c>
       <c r="D21" t="n">
-        <v>0.12398872214353</v>
+        <v>0.124013734188933</v>
       </c>
     </row>
     <row r="22">
@@ -1675,10 +1672,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>1.24338693883654</v>
+        <v>1.24344463218173</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0231491662220035</v>
+        <v>0.0231511545115636</v>
       </c>
     </row>
     <row r="23">
@@ -1689,10 +1686,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>1.15782568183839</v>
+        <v>1.15781211665459</v>
       </c>
       <c r="D23" t="n">
-        <v>0.388147454124298</v>
+        <v>0.388147147303828</v>
       </c>
     </row>
     <row r="24">
@@ -1703,10 +1700,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>1.10313487400028</v>
+        <v>1.1032148757848</v>
       </c>
       <c r="D24" t="n">
-        <v>0.091316681498599</v>
+        <v>0.091329827462734</v>
       </c>
     </row>
     <row r="25">
@@ -1717,10 +1714,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.984721758968322</v>
+        <v>0.984900229552156</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0159588214155303</v>
+        <v>0.0159645164405233</v>
       </c>
     </row>
     <row r="26">
@@ -1731,10 +1728,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.914810625981458</v>
+        <v>0.914748471908951</v>
       </c>
       <c r="D26" t="n">
-        <v>0.112719322261636</v>
+        <v>0.112713526040406</v>
       </c>
     </row>
     <row r="27">
@@ -1745,10 +1742,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.86366333890105</v>
+        <v>0.86376269509832</v>
       </c>
       <c r="D27" t="n">
-        <v>0.131172557706573</v>
+        <v>0.131190806078947</v>
       </c>
     </row>
     <row r="28">
@@ -1759,10 +1756,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.817268843767103</v>
+        <v>0.817270267623302</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0417804007434204</v>
+        <v>0.041781535892212</v>
       </c>
     </row>
     <row r="29">
@@ -1773,10 +1770,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.802075967957466</v>
+        <v>0.802285216131374</v>
       </c>
       <c r="D29" t="n">
-        <v>0.112447958531559</v>
+        <v>0.11247501721743</v>
       </c>
     </row>
     <row r="30">
@@ -1787,10 +1784,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.798940242138622</v>
+        <v>0.798941572377239</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0098569790692701</v>
+        <v>0.00985683283319847</v>
       </c>
     </row>
     <row r="31">
@@ -1801,10 +1798,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.773941617800593</v>
+        <v>0.774022120458686</v>
       </c>
       <c r="D31" t="n">
-        <v>0.106007082527806</v>
+        <v>0.106017431263646</v>
       </c>
     </row>
     <row r="32">
@@ -1815,10 +1812,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.771787233637991</v>
+        <v>0.771750035631288</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0649782963884106</v>
+        <v>0.064973686870251</v>
       </c>
     </row>
     <row r="33">
@@ -1829,10 +1826,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.719770124787197</v>
+        <v>0.719736577546547</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0138090172437913</v>
+        <v>0.0138080383445599</v>
       </c>
     </row>
     <row r="34">
@@ -1843,10 +1840,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.652556528371619</v>
+        <v>0.652649979416629</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0219046403388008</v>
+        <v>0.0219088248748368</v>
       </c>
     </row>
     <row r="35">
@@ -1857,10 +1854,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.637769836102387</v>
+        <v>0.637767957096375</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0637842852856246</v>
+        <v>0.0637833909765124</v>
       </c>
     </row>
     <row r="36">
@@ -1871,10 +1868,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.630804205125401</v>
+        <v>0.630698100890269</v>
       </c>
       <c r="D36" t="n">
-        <v>0.21514285032078</v>
+        <v>0.215099761008479</v>
       </c>
     </row>
     <row r="37">
@@ -1885,10 +1882,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.62971956727195</v>
+        <v>0.629724572415285</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0842390369455602</v>
+        <v>0.0842382831493277</v>
       </c>
     </row>
     <row r="38">
@@ -1899,10 +1896,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.606351233641925</v>
+        <v>0.606451476672876</v>
       </c>
       <c r="D38" t="n">
-        <v>0.138613051448962</v>
+        <v>0.138641218906441</v>
       </c>
     </row>
     <row r="39">
@@ -1913,10 +1910,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.604586252249659</v>
+        <v>0.604715810034171</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0537765721160326</v>
+        <v>0.0537875609895246</v>
       </c>
     </row>
     <row r="40">
@@ -1927,10 +1924,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.601069402914586</v>
+        <v>0.601109066988274</v>
       </c>
       <c r="D40" t="n">
-        <v>0.114916725818998</v>
+        <v>0.114931127079321</v>
       </c>
     </row>
     <row r="41">
@@ -1941,10 +1938,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.595909705076689</v>
+        <v>0.59586385463544</v>
       </c>
       <c r="D41" t="n">
-        <v>0.063667323956488</v>
+        <v>0.0636635563826351</v>
       </c>
     </row>
     <row r="42">
@@ -1955,10 +1952,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.595790906115076</v>
+        <v>0.595858744832856</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0320979855705018</v>
+        <v>0.0320984994887233</v>
       </c>
     </row>
     <row r="43">
@@ -1969,10 +1966,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.575433387141262</v>
+        <v>0.575438363007157</v>
       </c>
       <c r="D43" t="n">
-        <v>0.159362697032732</v>
+        <v>0.159352812235436</v>
       </c>
     </row>
     <row r="44">
@@ -1983,10 +1980,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.564366858239162</v>
+        <v>0.564317099847651</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0274906116577773</v>
+        <v>0.0274888222439849</v>
       </c>
     </row>
     <row r="45">
@@ -1997,10 +1994,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.55395138987645</v>
+        <v>0.553986634179406</v>
       </c>
       <c r="D45" t="n">
-        <v>0.017223332453407</v>
+        <v>0.0172252220198623</v>
       </c>
     </row>
     <row r="46">
@@ -2011,10 +2008,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.53536540901963</v>
+        <v>0.535455435235273</v>
       </c>
       <c r="D46" t="n">
-        <v>0.153722111742728</v>
+        <v>0.153748752402041</v>
       </c>
     </row>
     <row r="47">
@@ -2025,10 +2022,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.53364988089015</v>
+        <v>0.533610796502323</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0672478275891398</v>
+        <v>0.0672437902588174</v>
       </c>
     </row>
     <row r="48">
@@ -2039,10 +2036,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.510745963406598</v>
+        <v>0.51081480080556</v>
       </c>
       <c r="D48" t="n">
-        <v>0.153775147766951</v>
+        <v>0.15379211821604</v>
       </c>
     </row>
     <row r="49">
@@ -2053,10 +2050,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.446208066335029</v>
+        <v>0.446288047146405</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0337777799318058</v>
+        <v>0.0337854257187441</v>
       </c>
     </row>
     <row r="50">
@@ -2067,10 +2064,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.406629786645901</v>
+        <v>0.406617206121492</v>
       </c>
       <c r="D50" t="n">
-        <v>0.17598432539977</v>
+        <v>0.175977369525517</v>
       </c>
     </row>
     <row r="51">
@@ -2081,10 +2078,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.376478799111195</v>
+        <v>0.376460428719311</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0569277071811371</v>
+        <v>0.0569255066041069</v>
       </c>
     </row>
     <row r="52">
@@ -2095,10 +2092,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.375992656868376</v>
+        <v>0.376090634527935</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0119771154406029</v>
+        <v>0.0119805882665518</v>
       </c>
     </row>
     <row r="53">
@@ -2109,10 +2106,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.370900526634464</v>
+        <v>0.370954116562683</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0152327235651787</v>
+        <v>0.0152347047237327</v>
       </c>
     </row>
     <row r="54">
@@ -2123,10 +2120,10 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.319907100323329</v>
+        <v>0.319966284722752</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0792373807900135</v>
+        <v>0.0792516795713162</v>
       </c>
     </row>
     <row r="55">
@@ -2137,10 +2134,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.311547220728577</v>
+        <v>0.311533277594606</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0172972008546067</v>
+        <v>0.017295263988654</v>
       </c>
     </row>
     <row r="56">
@@ -2151,10 +2148,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.275900530996353</v>
+        <v>0.275951667170484</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0207687964413259</v>
+        <v>0.0207710775660657</v>
       </c>
     </row>
     <row r="57">
@@ -2165,10 +2162,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.275811181730556</v>
+        <v>0.275835974575014</v>
       </c>
       <c r="D57" t="n">
-        <v>0.194394119094118</v>
+        <v>0.1944109829825</v>
       </c>
     </row>
     <row r="58">
@@ -2179,10 +2176,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.257536867560212</v>
+        <v>0.257546713674983</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00630636905983868</v>
+        <v>0.00630700331476103</v>
       </c>
     </row>
     <row r="59">
@@ -2193,10 +2190,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.250044031462655</v>
+        <v>0.250047245262464</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0225874571938306</v>
+        <v>0.022589536277193</v>
       </c>
     </row>
     <row r="60">
@@ -2207,10 +2204,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.243050006533665</v>
+        <v>0.243042039167317</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0283158351811229</v>
+        <v>0.0283152930887118</v>
       </c>
     </row>
     <row r="61">
@@ -2221,10 +2218,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.240955188548261</v>
+        <v>0.240932634902632</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0196478778738606</v>
+        <v>0.019645659674528</v>
       </c>
     </row>
     <row r="62">
@@ -2235,10 +2232,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.237664046127159</v>
+        <v>0.237706516607937</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0263527254056439</v>
+        <v>0.026356340237113</v>
       </c>
     </row>
     <row r="63">
@@ -2249,10 +2246,10 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.236651365549334</v>
+        <v>0.236621238972088</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0245403392704892</v>
+        <v>0.0245344346007489</v>
       </c>
     </row>
     <row r="64">
@@ -2263,10 +2260,10 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.230585283865868</v>
+        <v>0.230564123421666</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0509844526870072</v>
+        <v>0.0509783767753283</v>
       </c>
     </row>
     <row r="65">
@@ -2277,10 +2274,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.213616869225842</v>
+        <v>0.213611075897443</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00739620060044716</v>
+        <v>0.00739593158911284</v>
       </c>
     </row>
     <row r="66">
@@ -2291,10 +2288,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.212468831178191</v>
+        <v>0.212488863275521</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00823134626836457</v>
+        <v>0.00823229156251807</v>
       </c>
     </row>
     <row r="67">
@@ -2305,10 +2302,10 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.19731301753291</v>
+        <v>0.197330800533047</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0198040810568668</v>
+        <v>0.0198051649674637</v>
       </c>
     </row>
     <row r="68">
@@ -2319,10 +2316,10 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.196655900357966</v>
+        <v>0.196690408970031</v>
       </c>
       <c r="D68" t="n">
-        <v>0.130102366468841</v>
+        <v>0.1301284571786</v>
       </c>
     </row>
     <row r="69">
@@ -2333,10 +2330,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.180419394007164</v>
+        <v>0.18040569029904</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0166865917056073</v>
+        <v>0.0166850776816214</v>
       </c>
     </row>
     <row r="70">
@@ -2347,10 +2344,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.180274979366738</v>
+        <v>0.180255950866786</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0482170531919115</v>
+        <v>0.048211338126906</v>
       </c>
     </row>
     <row r="71">
@@ -2361,10 +2358,10 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.175977435265221</v>
+        <v>0.176027089356245</v>
       </c>
       <c r="D71" t="n">
-        <v>0.029938940236214</v>
+        <v>0.0299476660505482</v>
       </c>
     </row>
     <row r="72">
@@ -2375,10 +2372,10 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.175302426010932</v>
+        <v>0.175282668877571</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0704758478739547</v>
+        <v>0.0704671562035202</v>
       </c>
     </row>
     <row r="73">
@@ -2389,10 +2386,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>0.168522161421196</v>
+        <v>0.168502071930805</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0229008601942342</v>
+        <v>0.0228979232440653</v>
       </c>
     </row>
     <row r="74">
@@ -2403,10 +2400,10 @@
         <v>77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.164740653782025</v>
+        <v>0.164729149218252</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0423817048114432</v>
+        <v>0.0423770396106077</v>
       </c>
     </row>
     <row r="75">
@@ -2417,10 +2414,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>0.161638211676001</v>
+        <v>0.161676597587428</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0265707855618042</v>
+        <v>0.0265770666322205</v>
       </c>
     </row>
     <row r="76">
@@ -2431,10 +2428,10 @@
         <v>79</v>
       </c>
       <c r="C76" t="n">
-        <v>0.159462823768081</v>
+        <v>0.15945461104189</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0288106145615336</v>
+        <v>0.0288087319627314</v>
       </c>
     </row>
     <row r="77">
@@ -2445,10 +2442,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>0.158651012341907</v>
+        <v>0.158673366659809</v>
       </c>
       <c r="D77" t="n">
-        <v>0.045737570407468</v>
+        <v>0.0457539772131932</v>
       </c>
     </row>
     <row r="78">
@@ -2459,10 +2456,10 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>0.157965501214959</v>
+        <v>0.157974490073735</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00578971777631656</v>
+        <v>0.00578989221271273</v>
       </c>
     </row>
     <row r="79">
@@ -2473,10 +2470,10 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>0.154868671220779</v>
+        <v>0.154857732662612</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00607966611977489</v>
+        <v>0.00607919411399602</v>
       </c>
     </row>
     <row r="80">
@@ -2487,10 +2484,10 @@
         <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>0.139344736377798</v>
+        <v>0.139376141658683</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0544590372234896</v>
+        <v>0.0544750660978915</v>
       </c>
     </row>
     <row r="81">
@@ -2501,10 +2498,10 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>0.137410891541032</v>
+        <v>0.137395260037261</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0449355261351212</v>
+        <v>0.0449289816918205</v>
       </c>
     </row>
     <row r="82">
@@ -2515,10 +2512,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.135808327999466</v>
+        <v>0.135806111433529</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0204445409249088</v>
+        <v>0.0204457783616086</v>
       </c>
     </row>
     <row r="83">
@@ -2529,10 +2526,10 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>0.129248324908248</v>
+        <v>0.129245902493879</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0166367019184684</v>
+        <v>0.0166375705717833</v>
       </c>
     </row>
     <row r="84">
@@ -2543,10 +2540,10 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>0.128756181595337</v>
+        <v>0.128755250363117</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00720842941131791</v>
+        <v>0.00720834530157348</v>
       </c>
     </row>
     <row r="85">
@@ -2557,10 +2554,10 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>0.124058566154433</v>
+        <v>0.124092666587563</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0269130501291136</v>
+        <v>0.0269210790674442</v>
       </c>
     </row>
     <row r="86">
@@ -2571,10 +2568,10 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1230162691844</v>
+        <v>0.123026273004742</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0227754272612695</v>
+        <v>0.0227784379571152</v>
       </c>
     </row>
     <row r="87">
@@ -2585,10 +2582,10 @@
         <v>90</v>
       </c>
       <c r="C87" t="n">
-        <v>0.109538699242387</v>
+        <v>0.10955527823509</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00492959743717087</v>
+        <v>0.00492991799053148</v>
       </c>
     </row>
     <row r="88">
@@ -2599,10 +2596,10 @@
         <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>0.096861716502859</v>
+        <v>0.0968590850529563</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0098797210525114</v>
+        <v>0.00987867127821817</v>
       </c>
     </row>
     <row r="89">
@@ -2613,10 +2610,10 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0966520124424633</v>
+        <v>0.0966437513070919</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0513418994701479</v>
+        <v>0.0513390455805359</v>
       </c>
     </row>
     <row r="90">
@@ -2627,10 +2624,10 @@
         <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0957017874459538</v>
+        <v>0.0957086574341561</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0295079921162402</v>
+        <v>0.0295107728838257</v>
       </c>
     </row>
     <row r="91">
@@ -2641,10 +2638,10 @@
         <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0944790138494864</v>
+        <v>0.0944699190967785</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0199537934468467</v>
+        <v>0.0199518548574393</v>
       </c>
     </row>
     <row r="92">
@@ -2655,10 +2652,10 @@
         <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0909867244494149</v>
+        <v>0.0909959753767429</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00458128100520624</v>
+        <v>0.00458206968934786</v>
       </c>
     </row>
     <row r="93">
@@ -2669,10 +2666,10 @@
         <v>96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0854309559855238</v>
+        <v>0.0854199033065721</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0133012523857728</v>
+        <v>0.0132973407545517</v>
       </c>
     </row>
     <row r="94">
@@ -2683,10 +2680,10 @@
         <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0812239280245435</v>
+        <v>0.0812389184245935</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0116606661657457</v>
+        <v>0.0116625794027242</v>
       </c>
     </row>
     <row r="95">
@@ -2697,10 +2694,10 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0807774595228796</v>
+        <v>0.0808056960315726</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0331322982602861</v>
+        <v>0.0331435943279887</v>
       </c>
     </row>
     <row r="96">
@@ -2711,7 +2708,7 @@
         <v>99</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0735733971407114</v>
+        <v>0.0735541085857273</v>
       </c>
       <c r="D96"/>
     </row>
@@ -2723,10 +2720,10 @@
         <v>100</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0692411801897809</v>
+        <v>0.0692410464152097</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0243421446622777</v>
+        <v>0.0243414152156006</v>
       </c>
     </row>
     <row r="98">
@@ -2737,10 +2734,10 @@
         <v>101</v>
       </c>
       <c r="C98" t="n">
-        <v>0.067218041652683</v>
+        <v>0.0672108440905825</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00668684478327204</v>
+        <v>0.00668616124790953</v>
       </c>
     </row>
     <row r="99">
@@ -2751,10 +2748,10 @@
         <v>102</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0664441814382869</v>
+        <v>0.0664443737029301</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0104633091800518</v>
+        <v>0.0104637243687183</v>
       </c>
     </row>
     <row r="100">
@@ -2765,10 +2762,10 @@
         <v>103</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0621268560316559</v>
+        <v>0.0621190368979436</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0269665544504838</v>
+        <v>0.0269607735447785</v>
       </c>
     </row>
     <row r="101">
@@ -2779,10 +2776,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0618822012945276</v>
+        <v>0.0618992598454842</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0269920541253336</v>
+        <v>0.0269964732951769</v>
       </c>
     </row>
     <row r="102">
@@ -2793,7 +2790,7 @@
         <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>0.06156481136528</v>
+        <v>0.0615545147950379</v>
       </c>
       <c r="D102"/>
     </row>
@@ -2805,10 +2802,10 @@
         <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0608275687915307</v>
+        <v>0.060837864982583</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00654315633753597</v>
+        <v>0.00654416720363598</v>
       </c>
     </row>
     <row r="104">
@@ -2819,10 +2816,10 @@
         <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0598622299888665</v>
+        <v>0.059880721200669</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0324982296524552</v>
+        <v>0.032507781909718</v>
       </c>
     </row>
     <row r="105">
@@ -2833,10 +2830,10 @@
         <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0575685432085077</v>
+        <v>0.0575790883844144</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00404441216473035</v>
+        <v>0.00404498640104643</v>
       </c>
     </row>
     <row r="106">
@@ -2847,10 +2844,10 @@
         <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0568111303713975</v>
+        <v>0.0568213935272874</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00906707020991561</v>
+        <v>0.00907161235571958</v>
       </c>
     </row>
     <row r="107">
@@ -2861,10 +2858,10 @@
         <v>110</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0558564601377837</v>
+        <v>0.0558554742148481</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0072784081124607</v>
+        <v>0.00727819198305638</v>
       </c>
     </row>
     <row r="108">
@@ -2875,7 +2872,7 @@
         <v>111</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0544758250586496</v>
+        <v>0.0544708843384869</v>
       </c>
       <c r="D108"/>
     </row>
@@ -2887,10 +2884,10 @@
         <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0542160009499028</v>
+        <v>0.0542131170146395</v>
       </c>
       <c r="D109" t="n">
-        <v>0.00238333965515841</v>
+        <v>0.00238309959775375</v>
       </c>
     </row>
     <row r="110">
@@ -2901,10 +2898,10 @@
         <v>113</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0536724040175098</v>
+        <v>0.0536773097806045</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00714669154979342</v>
+        <v>0.00714732142064009</v>
       </c>
     </row>
     <row r="111">
@@ -2915,7 +2912,7 @@
         <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0501224932314737</v>
+        <v>0.0501269411871334</v>
       </c>
       <c r="D111"/>
     </row>
@@ -2927,10 +2924,10 @@
         <v>115</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0485921647928521</v>
+        <v>0.0486074969556113</v>
       </c>
       <c r="D112" t="n">
-        <v>0.0249573550256908</v>
+        <v>0.024964666253421</v>
       </c>
     </row>
     <row r="113">
@@ -2941,10 +2938,10 @@
         <v>116</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0477312890621391</v>
+        <v>0.0477467173854783</v>
       </c>
       <c r="D113" t="n">
-        <v>0.0221630067458348</v>
+        <v>0.0221702783935531</v>
       </c>
     </row>
     <row r="114">
@@ -2955,10 +2952,10 @@
         <v>117</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0453171919217174</v>
+        <v>0.0453260039524754</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00635056515712386</v>
+        <v>0.00635236227949096</v>
       </c>
     </row>
     <row r="115">
@@ -2969,10 +2966,10 @@
         <v>118</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0444333676544535</v>
+        <v>0.044441119444064</v>
       </c>
       <c r="D115" t="n">
-        <v>0.0027361000168165</v>
+        <v>0.00273663123169244</v>
       </c>
     </row>
     <row r="116">
@@ -2983,10 +2980,10 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>0.041275304519162</v>
+        <v>0.0412794290949981</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0080909810456354</v>
+        <v>0.00809159300126105</v>
       </c>
     </row>
     <row r="117">
@@ -2997,10 +2994,10 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0394546465321653</v>
+        <v>0.0394545630763963</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0048306054789954</v>
+        <v>0.00483024384608776</v>
       </c>
     </row>
     <row r="118">
@@ -3011,10 +3008,10 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0389512789955663</v>
+        <v>0.0389592454737091</v>
       </c>
       <c r="D118" t="n">
-        <v>0.0116710061553571</v>
+        <v>0.0116713660199932</v>
       </c>
     </row>
     <row r="119">
@@ -3025,10 +3022,10 @@
         <v>122</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0386115517498696</v>
+        <v>0.0386107791539894</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0187662986193951</v>
+        <v>0.0187667032085123</v>
       </c>
     </row>
     <row r="120">
@@ -3039,10 +3036,10 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0382546547758575</v>
+        <v>0.038269810914149</v>
       </c>
       <c r="D120" t="n">
-        <v>0.018637517857858</v>
+        <v>0.0186451825301352</v>
       </c>
     </row>
     <row r="121">
@@ -3053,10 +3050,10 @@
         <v>124</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0379787166826076</v>
+        <v>0.0379799407001521</v>
       </c>
       <c r="D121" t="n">
-        <v>0.00304539560801592</v>
+        <v>0.00304531061956671</v>
       </c>
     </row>
     <row r="122">
@@ -3067,10 +3064,10 @@
         <v>125</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0377400630155701</v>
+        <v>0.0377351700480953</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0150416992735418</v>
+        <v>0.0150409117416798</v>
       </c>
     </row>
     <row r="123">
@@ -3081,10 +3078,10 @@
         <v>126</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0360922136210034</v>
+        <v>0.0360885361652888</v>
       </c>
       <c r="D123" t="n">
-        <v>0.00329405287532919</v>
+        <v>0.00329315460379549</v>
       </c>
     </row>
     <row r="124">
@@ -3095,10 +3092,10 @@
         <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0357424290263582</v>
+        <v>0.0357480677974404</v>
       </c>
       <c r="D124" t="n">
-        <v>0.00168638120545988</v>
+        <v>0.00168680940639728</v>
       </c>
     </row>
     <row r="125">
@@ -3109,10 +3106,10 @@
         <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0334059012734066</v>
+        <v>0.033409611077779</v>
       </c>
       <c r="D125" t="n">
-        <v>0.00717816163877701</v>
+        <v>0.0071774049476777</v>
       </c>
     </row>
     <row r="126">
@@ -3123,10 +3120,10 @@
         <v>129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0326582679579259</v>
+        <v>0.0326619136604909</v>
       </c>
       <c r="D126" t="n">
-        <v>0.00209412826448036</v>
+        <v>0.00209457650402667</v>
       </c>
     </row>
     <row r="127">
@@ -3137,7 +3134,7 @@
         <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0316309736631204</v>
+        <v>0.0316297890797849</v>
       </c>
       <c r="D127"/>
     </row>
@@ -3149,10 +3146,10 @@
         <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0313758170533332</v>
+        <v>0.0313841297664091</v>
       </c>
       <c r="D128" t="n">
-        <v>0.00523947935992204</v>
+        <v>0.00524152469478577</v>
       </c>
     </row>
     <row r="129">
@@ -3163,10 +3160,10 @@
         <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0298202618941446</v>
+        <v>0.0298250290235258</v>
       </c>
       <c r="D129" t="n">
-        <v>0.00668946759658577</v>
+        <v>0.00669114910307872</v>
       </c>
     </row>
     <row r="130">
@@ -3177,10 +3174,10 @@
         <v>133</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0297184103989921</v>
+        <v>0.0297134464866567</v>
       </c>
       <c r="D130" t="n">
-        <v>0.0166486551989316</v>
+        <v>0.0166461770143964</v>
       </c>
     </row>
     <row r="131">
@@ -3191,10 +3188,10 @@
         <v>134</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0295457685029536</v>
+        <v>0.0295461004520193</v>
       </c>
       <c r="D131" t="n">
-        <v>0.00598291523636964</v>
+        <v>0.00598137732196592</v>
       </c>
     </row>
     <row r="132">
@@ -3205,10 +3202,10 @@
         <v>135</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0294915921757449</v>
+        <v>0.0294900037062563</v>
       </c>
       <c r="D132" t="n">
-        <v>0.00836889204896852</v>
+        <v>0.00836874621831844</v>
       </c>
     </row>
     <row r="133">
@@ -3219,7 +3216,7 @@
         <v>136</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0289973929406735</v>
+        <v>0.028990242796974</v>
       </c>
       <c r="D133"/>
     </row>
@@ -3231,10 +3228,10 @@
         <v>137</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0284435163974768</v>
+        <v>0.0284444381231001</v>
       </c>
       <c r="D134" t="n">
-        <v>0.00324576006104418</v>
+        <v>0.00324535478653873</v>
       </c>
     </row>
     <row r="135">
@@ -3245,10 +3242,10 @@
         <v>138</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0256712998428392</v>
+        <v>0.0256698708611311</v>
       </c>
       <c r="D135" t="n">
-        <v>0.0038681151108631</v>
+        <v>0.00386771393409036</v>
       </c>
     </row>
     <row r="136">
@@ -3259,10 +3256,10 @@
         <v>139</v>
       </c>
       <c r="C136" t="n">
-        <v>0.025072804232208</v>
+        <v>0.0250756896867032</v>
       </c>
       <c r="D136" t="n">
-        <v>0.00708558778096048</v>
+        <v>0.0070866330128786</v>
       </c>
     </row>
     <row r="137">
@@ -3273,7 +3270,7 @@
         <v>140</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0238614771212843</v>
+        <v>0.0238649997222071</v>
       </c>
       <c r="D137"/>
     </row>
@@ -3285,10 +3282,10 @@
         <v>141</v>
       </c>
       <c r="C138" t="n">
-        <v>0.022992766660175</v>
+        <v>0.0229926120135944</v>
       </c>
       <c r="D138" t="n">
-        <v>0.00798052391016498</v>
+        <v>0.00798147260399848</v>
       </c>
     </row>
     <row r="139">
@@ -3299,10 +3296,10 @@
         <v>142</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0216161878598986</v>
+        <v>0.0216140206011366</v>
       </c>
       <c r="D139" t="n">
-        <v>0.00500467422972252</v>
+        <v>0.00500333103498446</v>
       </c>
     </row>
     <row r="140">
@@ -3313,10 +3310,10 @@
         <v>143</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0213901475531446</v>
+        <v>0.0213931882633608</v>
       </c>
       <c r="D140" t="n">
-        <v>0.00171817471322535</v>
+        <v>0.0017184961342313</v>
       </c>
     </row>
     <row r="141">
@@ -3327,10 +3324,10 @@
         <v>144</v>
       </c>
       <c r="C141" t="n">
-        <v>0.02026061280494</v>
+        <v>0.0202617002389221</v>
       </c>
       <c r="D141" t="n">
-        <v>0.00548173383527849</v>
+        <v>0.00548156715756894</v>
       </c>
     </row>
     <row r="142">
@@ -3341,10 +3338,10 @@
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0198953254458936</v>
+        <v>0.0198928502501975</v>
       </c>
       <c r="D142" t="n">
-        <v>0.00562941666221915</v>
+        <v>0.00562952466649978</v>
       </c>
     </row>
     <row r="143">
@@ -3355,10 +3352,10 @@
         <v>146</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0197244616446968</v>
+        <v>0.0197225605249409</v>
       </c>
       <c r="D143" t="n">
-        <v>0.00670892909133827</v>
+        <v>0.0067068795102041</v>
       </c>
     </row>
     <row r="144">
@@ -3369,10 +3366,10 @@
         <v>147</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0194635817921377</v>
+        <v>0.0194313573189654</v>
       </c>
       <c r="D144" t="n">
-        <v>0.00294014730992919</v>
+        <v>0.0134430571653996</v>
       </c>
     </row>
     <row r="145">
@@ -3383,10 +3380,10 @@
         <v>148</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0194367992385843</v>
+        <v>0.0192297978235458</v>
       </c>
       <c r="D145" t="n">
-        <v>0.0134471690570031</v>
+        <v>0.0045175304610228</v>
       </c>
     </row>
     <row r="146">
@@ -3397,11 +3394,9 @@
         <v>149</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0192247614287088</v>
-      </c>
-      <c r="D146" t="n">
-        <v>0.00451442471632134</v>
-      </c>
+        <v>0.0191584272113622</v>
+      </c>
+      <c r="D146"/>
     </row>
     <row r="147">
       <c r="A147" t="s">
@@ -3411,9 +3406,11 @@
         <v>150</v>
       </c>
       <c r="C147" t="n">
-        <v>0.019155860253592</v>
-      </c>
-      <c r="D147"/>
+        <v>0.0190963875430284</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.0127783505917011</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
@@ -3423,11 +3420,9 @@
         <v>151</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0191004059207158</v>
-      </c>
-      <c r="D148" t="n">
-        <v>0.0127808770907428</v>
-      </c>
+        <v>0.0187500873352738</v>
+      </c>
+      <c r="D148"/>
     </row>
     <row r="149">
       <c r="A149" t="s">
@@ -3437,9 +3432,11 @@
         <v>152</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0187503434987516</v>
-      </c>
-      <c r="D149"/>
+        <v>0.0185417517972967</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.00370307410304447</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
@@ -3449,10 +3446,10 @@
         <v>153</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0185365275940344</v>
+        <v>0.0185310878614685</v>
       </c>
       <c r="D150" t="n">
-        <v>0.00370216387902646</v>
+        <v>0.00566923770485209</v>
       </c>
     </row>
     <row r="151">
@@ -3463,10 +3460,10 @@
         <v>154</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0185326380115681</v>
+        <v>0.0184837111048984</v>
       </c>
       <c r="D151" t="n">
-        <v>0.00566939698922459</v>
+        <v>0.00318220665807674</v>
       </c>
     </row>
     <row r="152">
@@ -3477,10 +3474,10 @@
         <v>155</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0183543284382216</v>
+        <v>0.0183576322802629</v>
       </c>
       <c r="D152" t="n">
-        <v>0.00293734422480663</v>
+        <v>0.00293824038624759</v>
       </c>
     </row>
     <row r="153">
@@ -3491,10 +3488,10 @@
         <v>156</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0178994139860595</v>
+        <v>0.0179009714449529</v>
       </c>
       <c r="D153" t="n">
-        <v>0.00235547475936501</v>
+        <v>0.00235512932184248</v>
       </c>
     </row>
     <row r="154">
@@ -3505,10 +3502,10 @@
         <v>157</v>
       </c>
       <c r="C154" t="n">
-        <v>0.017822511384155</v>
+        <v>0.0178236579101984</v>
       </c>
       <c r="D154" t="n">
-        <v>0.00684052994845103</v>
+        <v>0.0068413147654906</v>
       </c>
     </row>
     <row r="155">
@@ -3519,10 +3516,10 @@
         <v>158</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0176228646727078</v>
+        <v>0.0176228204521005</v>
       </c>
       <c r="D155" t="n">
-        <v>0.00507237707616203</v>
+        <v>0.00507194153967515</v>
       </c>
     </row>
     <row r="156">
@@ -3533,10 +3530,10 @@
         <v>159</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0175083998172719</v>
+        <v>0.0175113489978963</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0102155469357067</v>
+        <v>0.0102185724492777</v>
       </c>
     </row>
     <row r="157">
@@ -3547,10 +3544,10 @@
         <v>160</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0169651362776617</v>
+        <v>0.0169664885266739</v>
       </c>
       <c r="D157" t="n">
-        <v>0.00942314338587107</v>
+        <v>0.00942379708993386</v>
       </c>
     </row>
     <row r="158">
@@ -3561,10 +3558,10 @@
         <v>161</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0165665652057967</v>
+        <v>0.016564924693143</v>
       </c>
       <c r="D158" t="n">
-        <v>0.00185358351927208</v>
+        <v>0.00185341504255475</v>
       </c>
     </row>
     <row r="159">
@@ -3575,10 +3572,10 @@
         <v>162</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0163720305170195</v>
+        <v>0.0163773060721655</v>
       </c>
       <c r="D159" t="n">
-        <v>0.0106598070644074</v>
+        <v>0.0106630716517072</v>
       </c>
     </row>
     <row r="160">
@@ -3589,10 +3586,10 @@
         <v>163</v>
       </c>
       <c r="C160" t="n">
-        <v>0.016284070387818</v>
+        <v>0.0162848852949877</v>
       </c>
       <c r="D160" t="n">
-        <v>0.00229361056036175</v>
+        <v>0.00229383266052794</v>
       </c>
     </row>
     <row r="161">
@@ -3603,10 +3600,10 @@
         <v>164</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0162728461641296</v>
+        <v>0.0162734993218378</v>
       </c>
       <c r="D161" t="n">
-        <v>0.00566254289653467</v>
+        <v>0.0056617618805572</v>
       </c>
     </row>
     <row r="162">
@@ -3617,10 +3614,10 @@
         <v>165</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0149113256045441</v>
+        <v>0.0149099596104707</v>
       </c>
       <c r="D162" t="n">
-        <v>0.00273498055236116</v>
+        <v>0.00273402095514348</v>
       </c>
     </row>
     <row r="163">
@@ -3631,10 +3628,10 @@
         <v>166</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0140552285037183</v>
+        <v>0.0140572890748737</v>
       </c>
       <c r="D163" t="n">
-        <v>0.00201327935472589</v>
+        <v>0.0020135781075336</v>
       </c>
     </row>
     <row r="164">
@@ -3645,10 +3642,10 @@
         <v>167</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0138320220356182</v>
+        <v>0.0138361234891033</v>
       </c>
       <c r="D164" t="n">
-        <v>0.00140852272491718</v>
+        <v>0.00140883061775872</v>
       </c>
     </row>
     <row r="165">
@@ -3659,10 +3656,10 @@
         <v>168</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0137511742857836</v>
+        <v>0.0137539223170942</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00312839997472917</v>
+        <v>0.00312905762647471</v>
       </c>
     </row>
     <row r="166">
@@ -3673,10 +3670,10 @@
         <v>169</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0125534607134918</v>
+        <v>0.0125530631684398</v>
       </c>
       <c r="D166" t="n">
-        <v>0.00189255182226881</v>
+        <v>0.0018923191647695</v>
       </c>
     </row>
     <row r="167">
@@ -3687,10 +3684,10 @@
         <v>170</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0117224792023053</v>
+        <v>0.0117248308191157</v>
       </c>
       <c r="D167" t="n">
-        <v>0.00182197464128326</v>
+        <v>0.00182313132018935</v>
       </c>
     </row>
     <row r="168">
@@ -3701,10 +3698,10 @@
         <v>171</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0117140332518071</v>
+        <v>0.0117169439499095</v>
       </c>
       <c r="D168" t="n">
-        <v>0.00488712138592374</v>
+        <v>0.00488855232754456</v>
       </c>
     </row>
     <row r="169">
@@ -3715,10 +3712,10 @@
         <v>172</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0115003840434814</v>
+        <v>0.0115021656173695</v>
       </c>
       <c r="D169" t="n">
-        <v>0.00583182022931677</v>
+        <v>0.0058329493609131</v>
       </c>
     </row>
     <row r="170">
@@ -3729,10 +3726,10 @@
         <v>173</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0114864371120666</v>
+        <v>0.0114842257669918</v>
       </c>
       <c r="D170" t="n">
-        <v>0.00438291868901427</v>
+        <v>0.00438250764268453</v>
       </c>
     </row>
     <row r="171">
@@ -3743,7 +3740,7 @@
         <v>174</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0109848476703093</v>
+        <v>0.0109872419243315</v>
       </c>
       <c r="D171"/>
     </row>
@@ -3755,7 +3752,7 @@
         <v>175</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0108504903788316</v>
+        <v>0.0108469445185916</v>
       </c>
       <c r="D172"/>
     </row>
@@ -3767,7 +3764,7 @@
         <v>176</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0102178775734249</v>
+        <v>0.0102195496273655</v>
       </c>
       <c r="D173"/>
     </row>
@@ -3779,10 +3776,10 @@
         <v>177</v>
       </c>
       <c r="C174" t="n">
-        <v>0.00962232693237529</v>
+        <v>0.00962431316762125</v>
       </c>
       <c r="D174" t="n">
-        <v>0.00480576537735567</v>
+        <v>0.00480803767080995</v>
       </c>
     </row>
     <row r="175">
@@ -3793,10 +3790,10 @@
         <v>178</v>
       </c>
       <c r="C175" t="n">
-        <v>0.00918941640387954</v>
+        <v>0.0091908686092706</v>
       </c>
       <c r="D175" t="n">
-        <v>0.00108399805345758</v>
+        <v>0.00108462697519654</v>
       </c>
     </row>
     <row r="176">
@@ -3807,7 +3804,7 @@
         <v>179</v>
       </c>
       <c r="C176" t="n">
-        <v>0.00861631421020671</v>
+        <v>0.00861351645857161</v>
       </c>
       <c r="D176"/>
     </row>
@@ -3819,10 +3816,10 @@
         <v>180</v>
       </c>
       <c r="C177" t="n">
-        <v>0.00796747628936924</v>
+        <v>0.00797045891159778</v>
       </c>
       <c r="D177" t="n">
-        <v>0.00533713302399469</v>
+        <v>0.00533897818305983</v>
       </c>
     </row>
     <row r="178">
@@ -3833,10 +3830,10 @@
         <v>181</v>
       </c>
       <c r="C178" t="n">
-        <v>0.00781217081803749</v>
+        <v>0.00781499872210221</v>
       </c>
       <c r="D178" t="n">
-        <v>0.000517222988787047</v>
+        <v>0.000518019480477547</v>
       </c>
     </row>
     <row r="179">
@@ -3847,7 +3844,7 @@
         <v>182</v>
       </c>
       <c r="C179" t="n">
-        <v>0.00779227838199572</v>
+        <v>0.00779161582114557</v>
       </c>
       <c r="D179"/>
     </row>
@@ -3859,10 +3856,10 @@
         <v>183</v>
       </c>
       <c r="C180" t="n">
-        <v>0.00775543847949377</v>
+        <v>0.00775440312841173</v>
       </c>
       <c r="D180" t="n">
-        <v>0.00349494850164058</v>
+        <v>0.00349421616357603</v>
       </c>
     </row>
     <row r="181">
@@ -3873,7 +3870,7 @@
         <v>184</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0077399357150925</v>
+        <v>0.00773785181134503</v>
       </c>
       <c r="D181"/>
     </row>
@@ -3885,10 +3882,10 @@
         <v>185</v>
       </c>
       <c r="C182" t="n">
-        <v>0.00764347406992903</v>
+        <v>0.00764209855422093</v>
       </c>
       <c r="D182" t="n">
-        <v>0.00492737014416636</v>
+        <v>0.00492660482862357</v>
       </c>
     </row>
     <row r="183">
@@ -3899,7 +3896,7 @@
         <v>186</v>
       </c>
       <c r="C183" t="n">
-        <v>0.00759891056795834</v>
+        <v>0.00760049809622443</v>
       </c>
       <c r="D183"/>
     </row>
@@ -3911,10 +3908,10 @@
         <v>187</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0073785379385123</v>
+        <v>0.00738183187041376</v>
       </c>
       <c r="D184" t="n">
-        <v>0.00240345867588676</v>
+        <v>0.00240454992335033</v>
       </c>
     </row>
     <row r="185">
@@ -3925,10 +3922,10 @@
         <v>188</v>
       </c>
       <c r="C185" t="n">
-        <v>0.00680515791752045</v>
+        <v>0.00680692353834207</v>
       </c>
       <c r="D185" t="n">
-        <v>0.00447894519954264</v>
+        <v>0.00448033831181793</v>
       </c>
     </row>
     <row r="186">
@@ -3939,10 +3936,10 @@
         <v>189</v>
       </c>
       <c r="C186" t="n">
-        <v>0.00667241202449307</v>
+        <v>0.00667056956720536</v>
       </c>
       <c r="D186" t="n">
-        <v>0.00213848825754954</v>
+        <v>0.00213724381577853</v>
       </c>
     </row>
     <row r="187">
@@ -3953,7 +3950,7 @@
         <v>190</v>
       </c>
       <c r="C187" t="n">
-        <v>0.00654644511804976</v>
+        <v>0.00654815647051074</v>
       </c>
       <c r="D187"/>
     </row>
@@ -3965,10 +3962,10 @@
         <v>191</v>
       </c>
       <c r="C188" t="n">
-        <v>0.00648132239447165</v>
+        <v>0.00648167349558177</v>
       </c>
       <c r="D188" t="n">
-        <v>0.00122466014140182</v>
+        <v>0.00122443733015672</v>
       </c>
     </row>
     <row r="189">
@@ -3979,10 +3976,10 @@
         <v>192</v>
       </c>
       <c r="C189" t="n">
-        <v>0.00629890097680364</v>
+        <v>0.00630171957848078</v>
       </c>
       <c r="D189" t="n">
-        <v>0.002228115950553</v>
+        <v>0.00222886178671014</v>
       </c>
     </row>
     <row r="190">
@@ -3993,10 +3990,10 @@
         <v>193</v>
       </c>
       <c r="C190" t="n">
-        <v>0.00617037805902535</v>
+        <v>0.00616903133528503</v>
       </c>
       <c r="D190" t="n">
-        <v>0.00362955849553183</v>
+        <v>0.00362821786694141</v>
       </c>
     </row>
     <row r="191">
@@ -4007,7 +4004,7 @@
         <v>194</v>
       </c>
       <c r="C191" t="n">
-        <v>0.00591344335439638</v>
+        <v>0.00591442986738659</v>
       </c>
       <c r="D191"/>
     </row>
@@ -4019,10 +4016,10 @@
         <v>195</v>
       </c>
       <c r="C192" t="n">
-        <v>0.00558355119579296</v>
+        <v>0.00558395893937707</v>
       </c>
       <c r="D192" t="n">
-        <v>0.00115410349329897</v>
+        <v>0.00115438021349579</v>
       </c>
     </row>
     <row r="193">
@@ -4033,10 +4030,10 @@
         <v>196</v>
       </c>
       <c r="C193" t="n">
-        <v>0.00552248475107254</v>
+        <v>0.00552275239102976</v>
       </c>
       <c r="D193" t="n">
-        <v>0.00185537327718893</v>
+        <v>0.0018554565067699</v>
       </c>
     </row>
     <row r="194">
@@ -4047,7 +4044,7 @@
         <v>197</v>
       </c>
       <c r="C194" t="n">
-        <v>0.00543441349094345</v>
+        <v>0.00543327530447121</v>
       </c>
       <c r="D194"/>
     </row>
@@ -4059,10 +4056,10 @@
         <v>198</v>
       </c>
       <c r="C195" t="n">
-        <v>0.00539629558277401</v>
+        <v>0.00539634031839956</v>
       </c>
       <c r="D195" t="n">
-        <v>0.00123235214220535</v>
+        <v>0.00123234364749038</v>
       </c>
     </row>
     <row r="196">
@@ -4073,10 +4070,10 @@
         <v>199</v>
       </c>
       <c r="C196" t="n">
-        <v>0.00484797558595769</v>
+        <v>0.00484892494588496</v>
       </c>
       <c r="D196" t="n">
-        <v>0.000449392379049456</v>
+        <v>0.000449703028565515</v>
       </c>
     </row>
     <row r="197">
@@ -4087,7 +4084,7 @@
         <v>200</v>
       </c>
       <c r="C197" t="n">
-        <v>0.00483597344577606</v>
+        <v>0.00483387324479411</v>
       </c>
       <c r="D197"/>
     </row>
@@ -4099,10 +4096,10 @@
         <v>201</v>
       </c>
       <c r="C198" t="n">
-        <v>0.00403016308969273</v>
+        <v>0.00403241181770546</v>
       </c>
       <c r="D198" t="n">
-        <v>0.000879205721231911</v>
+        <v>0.000879584697602053</v>
       </c>
     </row>
     <row r="199">
@@ -4113,7 +4110,7 @@
         <v>202</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0039226994826961</v>
+        <v>0.00392238443814464</v>
       </c>
       <c r="D199"/>
     </row>
@@ -4125,10 +4122,10 @@
         <v>203</v>
       </c>
       <c r="C200" t="n">
-        <v>0.00390819689664329</v>
+        <v>0.00390983209701353</v>
       </c>
       <c r="D200" t="n">
-        <v>0.000195691883627747</v>
+        <v>0.000196112370168056</v>
       </c>
     </row>
     <row r="201">
@@ -4139,10 +4136,10 @@
         <v>204</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0034267777182468</v>
+        <v>0.00342706683545743</v>
       </c>
       <c r="D201" t="n">
-        <v>0.000356041595137824</v>
+        <v>0.000356207481303227</v>
       </c>
     </row>
     <row r="202">
@@ -4153,10 +4150,10 @@
         <v>205</v>
       </c>
       <c r="C202" t="n">
-        <v>0.00330847884580842</v>
+        <v>0.00330915258669033</v>
       </c>
       <c r="D202" t="n">
-        <v>0.00170560999265008</v>
+        <v>0.00170541909933715</v>
       </c>
     </row>
     <row r="203">
@@ -4167,7 +4164,7 @@
         <v>206</v>
       </c>
       <c r="C203" t="n">
-        <v>0.00311466650806061</v>
+        <v>0.00311398034450118</v>
       </c>
       <c r="D203"/>
     </row>
@@ -4179,10 +4176,10 @@
         <v>207</v>
       </c>
       <c r="C204" t="n">
-        <v>0.00297825329442218</v>
+        <v>0.00297807070402398</v>
       </c>
       <c r="D204" t="n">
-        <v>0.00121569405166059</v>
+        <v>0.00121493044947482</v>
       </c>
     </row>
     <row r="205">
@@ -4193,10 +4190,10 @@
         <v>208</v>
       </c>
       <c r="C205" t="n">
-        <v>0.00277860658297497</v>
+        <v>0.00278017693654534</v>
       </c>
       <c r="D205" t="n">
-        <v>0.000569364724210868</v>
+        <v>0.000569547602535358</v>
       </c>
     </row>
     <row r="206">
@@ -4207,10 +4204,10 @@
         <v>209</v>
       </c>
       <c r="C206" t="n">
-        <v>0.00277282777473937</v>
+        <v>0.00277334535265539</v>
       </c>
       <c r="D206" t="n">
-        <v>0.000314749625803942</v>
+        <v>0.000314727263899275</v>
       </c>
     </row>
     <row r="207">
@@ -4221,7 +4218,7 @@
         <v>210</v>
       </c>
       <c r="C207" t="n">
-        <v>0.00275271307684238</v>
+        <v>0.00275229518766117</v>
       </c>
       <c r="D207"/>
     </row>
@@ -4233,10 +4230,10 @@
         <v>211</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00269486942902258</v>
+        <v>0.00269369908193848</v>
       </c>
       <c r="D208" t="n">
-        <v>0.0005784574558708</v>
+        <v>0.000578206239248034</v>
       </c>
     </row>
     <row r="209">
@@ -4247,10 +4244,10 @@
         <v>212</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00266553086413415</v>
+        <v>0.00266576179172187</v>
       </c>
       <c r="D209" t="n">
-        <v>0.000251896828010007</v>
+        <v>0.000251605887793505</v>
       </c>
     </row>
     <row r="210">
@@ -4261,10 +4258,10 @@
         <v>213</v>
       </c>
       <c r="C210" t="n">
-        <v>0.0025260615499865</v>
+        <v>0.00252568655131178</v>
       </c>
       <c r="D210" t="n">
-        <v>0.000212051995630788</v>
+        <v>0.000211449346693792</v>
       </c>
     </row>
     <row r="211">
@@ -4275,7 +4272,7 @@
         <v>214</v>
       </c>
       <c r="C211" t="n">
-        <v>0.00231958028649142</v>
+        <v>0.00231857292264834</v>
       </c>
       <c r="D211"/>
     </row>
@@ -4287,7 +4284,7 @@
         <v>215</v>
       </c>
       <c r="C212" t="n">
-        <v>0.00227296086236</v>
+        <v>0.00227236253405944</v>
       </c>
       <c r="D212"/>
     </row>
@@ -4299,10 +4296,10 @@
         <v>216</v>
       </c>
       <c r="C213" t="n">
-        <v>0.00222017367174635</v>
+        <v>0.0022203203055645</v>
       </c>
       <c r="D213" t="n">
-        <v>0.000460644357379165</v>
+        <v>0.000459658832411616</v>
       </c>
     </row>
     <row r="214">
@@ -4313,10 +4310,10 @@
         <v>217</v>
       </c>
       <c r="C214" t="n">
-        <v>0.00201885999638503</v>
+        <v>0.00201909405813954</v>
       </c>
       <c r="D214" t="n">
-        <v>0.000623227681629198</v>
+        <v>0.000623280955641878</v>
       </c>
     </row>
     <row r="215">
@@ -4327,7 +4324,7 @@
         <v>218</v>
       </c>
       <c r="C215" t="n">
-        <v>0.00188394705026929</v>
+        <v>0.0018831288763299</v>
       </c>
       <c r="D215"/>
     </row>
@@ -4339,10 +4336,10 @@
         <v>219</v>
       </c>
       <c r="C216" t="n">
-        <v>0.00186688845288151</v>
+        <v>0.00186652201793077</v>
       </c>
       <c r="D216" t="n">
-        <v>0.000384790453031839</v>
+        <v>0.00038445819438664</v>
       </c>
     </row>
     <row r="217">
@@ -4353,7 +4350,7 @@
         <v>220</v>
       </c>
       <c r="C217" t="n">
-        <v>0.00164279293736062</v>
+        <v>0.00164380127485208</v>
       </c>
       <c r="D217"/>
     </row>
@@ -4365,10 +4362,10 @@
         <v>221</v>
       </c>
       <c r="C218" t="n">
-        <v>0.00162451189976915</v>
+        <v>0.00162380639517419</v>
       </c>
       <c r="D218" t="n">
-        <v>0.0000347329931698382</v>
+        <v>0.0000347179090782526</v>
       </c>
     </row>
     <row r="219">
@@ -4379,10 +4376,10 @@
         <v>222</v>
       </c>
       <c r="C219" t="n">
-        <v>0.00149821160054302</v>
+        <v>0.00149822744253058</v>
       </c>
       <c r="D219" t="n">
-        <v>0.000425557747763028</v>
+        <v>0.00042490164968056</v>
       </c>
     </row>
     <row r="220">
@@ -4393,7 +4390,7 @@
         <v>223</v>
       </c>
       <c r="C220" t="n">
-        <v>0.0014965446366289</v>
+        <v>0.00149683890921961</v>
       </c>
       <c r="D220"/>
     </row>
@@ -4405,10 +4402,10 @@
         <v>224</v>
       </c>
       <c r="C221" t="n">
-        <v>0.00148515371654911</v>
+        <v>0.0014857306427319</v>
       </c>
       <c r="D221" t="n">
-        <v>0.000138327611613312</v>
+        <v>0.00013819619213571</v>
       </c>
     </row>
     <row r="222">
@@ -4419,7 +4416,7 @@
         <v>225</v>
       </c>
       <c r="C222" t="n">
-        <v>0.0014532035748619</v>
+        <v>0.00145329450458777</v>
       </c>
       <c r="D222"/>
     </row>
@@ -4431,7 +4428,7 @@
         <v>226</v>
       </c>
       <c r="C223" t="n">
-        <v>0.0014358115846913</v>
+        <v>0.00143518803021279</v>
       </c>
       <c r="D223"/>
     </row>
@@ -4443,11 +4440,9 @@
         <v>227</v>
       </c>
       <c r="C224" t="n">
-        <v>0.00141391879195259</v>
-      </c>
-      <c r="D224" t="n">
-        <v>0.000352575557025008</v>
-      </c>
+        <v>0.00139480948152995</v>
+      </c>
+      <c r="D224"/>
     </row>
     <row r="225">
       <c r="A225" t="s">
@@ -4457,7 +4452,7 @@
         <v>228</v>
       </c>
       <c r="C225" t="n">
-        <v>0.00139435974869363</v>
+        <v>0.00138670044699392</v>
       </c>
       <c r="D225"/>
     </row>
@@ -4469,9 +4464,11 @@
         <v>229</v>
       </c>
       <c r="C226" t="n">
-        <v>0.00138685841108012</v>
-      </c>
-      <c r="D226"/>
+        <v>0.00132621593596831</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.000595938407639598</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
@@ -4481,11 +4478,9 @@
         <v>230</v>
       </c>
       <c r="C227" t="n">
-        <v>0.0013258475318235</v>
-      </c>
-      <c r="D227" t="n">
-        <v>0.000595529386284204</v>
-      </c>
+        <v>0.00131999530673519</v>
+      </c>
+      <c r="D227"/>
     </row>
     <row r="228">
       <c r="A228" t="s">
@@ -4495,9 +4490,11 @@
         <v>231</v>
       </c>
       <c r="C228" t="n">
-        <v>0.00131995759266029</v>
-      </c>
-      <c r="D228"/>
+        <v>0.00128144962202281</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.00013329477761492</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
@@ -4507,10 +4504,10 @@
         <v>232</v>
       </c>
       <c r="C229" t="n">
-        <v>0.00128045054789576</v>
+        <v>0.00124962443853551</v>
       </c>
       <c r="D229" t="n">
-        <v>0.000133274109538564</v>
+        <v>0.000438176144328127</v>
       </c>
     </row>
     <row r="230">
@@ -4521,10 +4518,10 @@
         <v>233</v>
       </c>
       <c r="C230" t="n">
-        <v>0.00124950058455702</v>
+        <v>0.00123946037469925</v>
       </c>
       <c r="D230" t="n">
-        <v>0.000438366521262312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -4535,11 +4532,9 @@
         <v>234</v>
       </c>
       <c r="C231" t="n">
-        <v>0.00123888758097048</v>
-      </c>
-      <c r="D231" t="n">
-        <v>0</v>
-      </c>
+        <v>0.00123373961745808</v>
+      </c>
+      <c r="D231"/>
     </row>
     <row r="232">
       <c r="A232" t="s">
@@ -4549,9 +4544,11 @@
         <v>235</v>
       </c>
       <c r="C232" t="n">
-        <v>0.00123255311809684</v>
-      </c>
-      <c r="D232"/>
+        <v>0.00112432319255408</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.000128295552853185</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
@@ -4561,11 +4558,9 @@
         <v>236</v>
       </c>
       <c r="C233" t="n">
-        <v>0.00112481168378119</v>
-      </c>
-      <c r="D233" t="n">
-        <v>0.000128351294167125</v>
-      </c>
+        <v>0.00108450005719563</v>
+      </c>
+      <c r="D233"/>
     </row>
     <row r="234">
       <c r="A234" t="s">
@@ -4575,7 +4570,7 @@
         <v>237</v>
       </c>
       <c r="C234" t="n">
-        <v>0.00108402663334917</v>
+        <v>0.00103790087927966</v>
       </c>
       <c r="D234"/>
     </row>
@@ -4587,7 +4582,7 @@
         <v>238</v>
       </c>
       <c r="C235" t="n">
-        <v>0.00103740720921775</v>
+        <v>0.00103045834073289</v>
       </c>
       <c r="D235"/>
     </row>
@@ -4599,9 +4594,11 @@
         <v>239</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0010309060499527</v>
-      </c>
-      <c r="D236"/>
+        <v>0.000984747824135944</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.000258106446224294</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
@@ -4611,11 +4608,9 @@
         <v>240</v>
       </c>
       <c r="C237" t="n">
-        <v>0.000984897845923116</v>
-      </c>
-      <c r="D237" t="n">
-        <v>0.000258415040812246</v>
-      </c>
+        <v>0.000958587856557375</v>
+      </c>
+      <c r="D237"/>
     </row>
     <row r="238">
       <c r="A238" t="s">
@@ -4625,7 +4620,7 @@
         <v>241</v>
       </c>
       <c r="C238" t="n">
-        <v>0.000958115292369664</v>
+        <v>0.00094709080074259</v>
       </c>
       <c r="D238"/>
     </row>
@@ -4637,7 +4632,7 @@
         <v>242</v>
       </c>
       <c r="C239" t="n">
-        <v>0.00094750228878313</v>
+        <v>0.000941592208831171</v>
       </c>
       <c r="D239"/>
     </row>
@@ -4649,9 +4644,11 @@
         <v>243</v>
       </c>
       <c r="C240" t="n">
-        <v>0.000942001307866549</v>
-      </c>
-      <c r="D240"/>
+        <v>0.000935538203595367</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.000004241554502773</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
@@ -4661,11 +4658,9 @@
         <v>244</v>
       </c>
       <c r="C241" t="n">
-        <v>0.000935555714065304</v>
-      </c>
-      <c r="D241" t="n">
-        <v>0.00000451843236937943</v>
-      </c>
+        <v>0.000922597073137179</v>
+      </c>
+      <c r="D241"/>
     </row>
     <row r="242">
       <c r="A242" t="s">
@@ -4675,9 +4670,11 @@
         <v>245</v>
       </c>
       <c r="C242" t="n">
-        <v>0.000922997919245635</v>
-      </c>
-      <c r="D242"/>
+        <v>0.000919209051858425</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.000204537183800384</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
@@ -4687,10 +4684,10 @@
         <v>246</v>
       </c>
       <c r="C243" t="n">
-        <v>0.000919275033170778</v>
+        <v>0.000897325766877627</v>
       </c>
       <c r="D243" t="n">
-        <v>0.000204861794556036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -4701,11 +4698,9 @@
         <v>247</v>
       </c>
       <c r="C244" t="n">
-        <v>0.000896382062083594</v>
-      </c>
-      <c r="D244" t="n">
-        <v>0</v>
-      </c>
+        <v>0.000839618322473947</v>
+      </c>
+      <c r="D244"/>
     </row>
     <row r="245">
       <c r="A245" t="s">
@@ -4715,9 +4710,11 @@
         <v>248</v>
       </c>
       <c r="C245" t="n">
-        <v>0.000839983116322694</v>
-      </c>
-      <c r="D245"/>
+        <v>0.00082506649337504</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.000286422749895584</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
@@ -4727,11 +4724,9 @@
         <v>249</v>
       </c>
       <c r="C246" t="n">
-        <v>0.000825147137487068</v>
-      </c>
-      <c r="D246" t="n">
-        <v>0.000286743647232442</v>
-      </c>
+        <v>0.000820123314788007</v>
+      </c>
+      <c r="D246"/>
     </row>
     <row r="247">
       <c r="A247" t="s">
@@ -4741,9 +4736,11 @@
         <v>250</v>
       </c>
       <c r="C247" t="n">
-        <v>0.000820479638527545</v>
-      </c>
-      <c r="D247"/>
+        <v>0.000651444288172053</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.0000151989036349364</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
@@ -4753,11 +4750,9 @@
         <v>251</v>
       </c>
       <c r="C248" t="n">
-        <v>0.00065094940846202</v>
-      </c>
-      <c r="D248" t="n">
-        <v>0.0000151269257583571</v>
-      </c>
+        <v>0.000648722762882562</v>
+      </c>
+      <c r="D248"/>
     </row>
     <row r="249">
       <c r="A249" t="s">
@@ -4767,7 +4762,7 @@
         <v>252</v>
       </c>
       <c r="C249" t="n">
-        <v>0.000648393397127043</v>
+        <v>0.000619730187349626</v>
       </c>
       <c r="D249"/>
     </row>
@@ -4779,9 +4774,11 @@
         <v>253</v>
       </c>
       <c r="C250" t="n">
-        <v>0.000619443790485241</v>
-      </c>
-      <c r="D250"/>
+        <v>0.000615064715424786</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
@@ -4791,11 +4788,9 @@
         <v>254</v>
       </c>
       <c r="C251" t="n">
-        <v>0.000615331946163757</v>
-      </c>
-      <c r="D251" t="n">
-        <v>0</v>
-      </c>
+        <v>0.000588460417186708</v>
+      </c>
+      <c r="D251"/>
     </row>
     <row r="252">
       <c r="A252" t="s">
@@ -4805,7 +4800,7 @@
         <v>255</v>
       </c>
       <c r="C252" t="n">
-        <v>0.000588716089001716</v>
+        <v>0.000560800833632297</v>
       </c>
       <c r="D252"/>
     </row>
@@ -4817,7 +4812,7 @@
         <v>256</v>
       </c>
       <c r="C253" t="n">
-        <v>0.000560266571534148</v>
+        <v>0.000560800833632297</v>
       </c>
       <c r="D253"/>
     </row>
@@ -4829,7 +4824,7 @@
         <v>257</v>
       </c>
       <c r="C254" t="n">
-        <v>0.000560266571534148</v>
+        <v>0.000542916524587076</v>
       </c>
       <c r="D254"/>
     </row>
@@ -4841,7 +4836,7 @@
         <v>258</v>
       </c>
       <c r="C255" t="n">
-        <v>0.000543152408682565</v>
+        <v>0.00051897821030605</v>
       </c>
       <c r="D255"/>
     </row>
@@ -4853,9 +4848,11 @@
         <v>259</v>
       </c>
       <c r="C256" t="n">
-        <v>0.000518703604608874</v>
-      </c>
-      <c r="D256"/>
+        <v>0.000483820546872432</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.0000248602222245858</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
@@ -4865,11 +4862,9 @@
         <v>260</v>
       </c>
       <c r="C257" t="n">
-        <v>0.000483419535093434</v>
-      </c>
-      <c r="D257" t="n">
-        <v>0.0000249103141059699</v>
-      </c>
+        <v>0.000470768333749366</v>
+      </c>
+      <c r="D257"/>
     </row>
     <row r="258">
       <c r="A258" t="s">
@@ -4879,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="C258" t="n">
-        <v>0.000470972871201373</v>
+        <v>0.000470768333749366</v>
       </c>
       <c r="D258"/>
     </row>
@@ -4891,7 +4886,7 @@
         <v>262</v>
       </c>
       <c r="C259" t="n">
-        <v>0.000470972871201373</v>
+        <v>0.000470768333749366</v>
       </c>
       <c r="D259"/>
     </row>
@@ -4903,7 +4898,7 @@
         <v>263</v>
       </c>
       <c r="C260" t="n">
-        <v>0.000470972871201373</v>
+        <v>0.000464769869846</v>
       </c>
       <c r="D260"/>
     </row>
@@ -4915,7 +4910,7 @@
         <v>264</v>
       </c>
       <c r="C261" t="n">
-        <v>0.000464582842863931</v>
+        <v>0.00041994801456807</v>
       </c>
       <c r="D261"/>
     </row>
@@ -4927,7 +4922,7 @@
         <v>265</v>
       </c>
       <c r="C262" t="n">
-        <v>0.000419685948110426</v>
+        <v>0.000410061657394003</v>
       </c>
       <c r="D262"/>
     </row>
@@ -4939,7 +4934,7 @@
         <v>266</v>
       </c>
       <c r="C263" t="n">
-        <v>0.000410239819263772</v>
+        <v>0.000389233657729537</v>
       </c>
       <c r="D263"/>
     </row>
@@ -4951,7 +4946,7 @@
         <v>267</v>
       </c>
       <c r="C264" t="n">
-        <v>0.000389013812090704</v>
+        <v>0.000389233657729537</v>
       </c>
       <c r="D264"/>
     </row>
@@ -4963,7 +4958,7 @@
         <v>268</v>
       </c>
       <c r="C265" t="n">
-        <v>0.000389013812090704</v>
+        <v>0.000388011748415889</v>
       </c>
       <c r="D265"/>
     </row>
@@ -4975,7 +4970,7 @@
         <v>269</v>
       </c>
       <c r="C266" t="n">
-        <v>0.000388180330133647</v>
+        <v>0.000353076250312025</v>
       </c>
       <c r="D266"/>
     </row>
@@ -4987,7 +4982,7 @@
         <v>270</v>
       </c>
       <c r="C267" t="n">
-        <v>0.00035322965340103</v>
+        <v>0.000353076250312025</v>
       </c>
       <c r="D267"/>
     </row>
@@ -4999,7 +4994,7 @@
         <v>271</v>
       </c>
       <c r="C268" t="n">
-        <v>0.00035322965340103</v>
+        <v>0.000353076250312025</v>
       </c>
       <c r="D268"/>
     </row>
@@ -5011,7 +5006,7 @@
         <v>272</v>
       </c>
       <c r="C269" t="n">
-        <v>0.00035322965340103</v>
+        <v>0.000353076250312025</v>
       </c>
       <c r="D269"/>
     </row>
@@ -5023,7 +5018,7 @@
         <v>273</v>
       </c>
       <c r="C270" t="n">
-        <v>0.00035322965340103</v>
+        <v>0.000337413594564346</v>
       </c>
       <c r="D270"/>
     </row>
@@ -5035,7 +5030,7 @@
         <v>274</v>
       </c>
       <c r="C271" t="n">
-        <v>0.000337560192608346</v>
+        <v>0.000336469391912891</v>
       </c>
       <c r="D271"/>
     </row>
@@ -5047,7 +5042,7 @@
         <v>275</v>
       </c>
       <c r="C272" t="n">
-        <v>0.00033617105601325</v>
+        <v>0.000336469391912891</v>
       </c>
       <c r="D272"/>
     </row>
@@ -5059,7 +5054,7 @@
         <v>276</v>
       </c>
       <c r="C273" t="n">
-        <v>0.00033617105601325</v>
+        <v>0.000307532357712393</v>
       </c>
       <c r="D273"/>
     </row>
@@ -5071,7 +5066,7 @@
         <v>277</v>
       </c>
       <c r="C274" t="n">
-        <v>0.000307665973081878</v>
+        <v>0.000268486801008074</v>
       </c>
       <c r="D274"/>
     </row>
@@ -5083,7 +5078,7 @@
         <v>278</v>
       </c>
       <c r="C275" t="n">
-        <v>0.000268603452027777</v>
+        <v>0.000259489105153025</v>
       </c>
       <c r="D275"/>
     </row>
@@ -5095,7 +5090,7 @@
         <v>279</v>
       </c>
       <c r="C276" t="n">
-        <v>0.000259324019572535</v>
+        <v>0.000224942396376231</v>
       </c>
       <c r="D276"/>
     </row>
@@ -5107,7 +5102,7 @@
         <v>280</v>
       </c>
       <c r="C277" t="n">
-        <v>0.000225040128405564</v>
+        <v>0.000224331441719407</v>
       </c>
       <c r="D277"/>
     </row>
@@ -5119,7 +5114,7 @@
         <v>281</v>
       </c>
       <c r="C278" t="n">
-        <v>0.000224095515520899</v>
+        <v>0.000224331441719407</v>
       </c>
       <c r="D278"/>
     </row>
@@ -5131,21 +5126,9 @@
         <v>282</v>
       </c>
       <c r="C279" t="n">
-        <v>0.000224095515520899</v>
+        <v>0.000205003058030782</v>
       </c>
       <c r="D279"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="s">
-        <v>4</v>
-      </c>
-      <c r="B280" t="s">
-        <v>283</v>
-      </c>
-      <c r="C280" t="n">
-        <v>0.000205092126899984</v>
-      </c>
-      <c r="D280"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5174,4061 +5157,4047 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>12.0996076308437</v>
+        <v>12.2938896280527</v>
       </c>
       <c r="D2" t="n">
-        <v>2.29176087600768</v>
+        <v>2.33014365957232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>8.67920809365492</v>
+        <v>8.8112952152606</v>
       </c>
       <c r="D3" t="n">
-        <v>2.28619312956589</v>
+        <v>2.321077297726</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>7.28910229183832</v>
+        <v>7.01655554723549</v>
       </c>
       <c r="D4" t="n">
-        <v>0.505959383921211</v>
+        <v>0.481512471046699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>6.43457936383208</v>
+        <v>6.4990922487162</v>
       </c>
       <c r="D5" t="n">
-        <v>0.518854068435167</v>
+        <v>0.523843098151598</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>5.36838357745397</v>
+        <v>5.42361890298193</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05326214873936</v>
+        <v>0.0537982409071878</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>5.12730700561128</v>
+        <v>5.16392767701285</v>
       </c>
       <c r="D7" t="n">
-        <v>0.20777085709091</v>
+        <v>0.209507277233078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>3.90933790171079</v>
+        <v>3.94923566979233</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0928377232261522</v>
+        <v>0.0937959125318528</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75020910738491</v>
+        <v>3.7855950722528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6982943447638</v>
+        <v>0.704970457773954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9219226913432</v>
+        <v>2.93883146395014</v>
       </c>
       <c r="D10" t="n">
-        <v>0.312052103141693</v>
+        <v>0.313060623653461</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>2.77062585861263</v>
+        <v>2.79764974060704</v>
       </c>
       <c r="D11" t="n">
-        <v>0.131127960896464</v>
+        <v>0.13240567627641</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>2.44593337876785</v>
+        <v>2.47014871151312</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0501965925298373</v>
+        <v>0.0506833935769615</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B13" t="s">
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>2.37709430440606</v>
+        <v>2.4018132193288</v>
       </c>
       <c r="D13" t="n">
-        <v>0.219121970170156</v>
+        <v>0.221402690727476</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="n">
-        <v>2.15844656988221</v>
+        <v>2.17991274678628</v>
       </c>
       <c r="D14" t="n">
-        <v>0.292743939258328</v>
+        <v>0.29551369988764</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>1.96056103238851</v>
+        <v>1.98238244503224</v>
       </c>
       <c r="D15" t="n">
-        <v>0.276209985670932</v>
+        <v>0.279390314080453</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B16" t="s">
         <v>106</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4985026333635</v>
+        <v>1.51286599347572</v>
       </c>
       <c r="D16" t="n">
-        <v>0.169130225818292</v>
+        <v>0.170703299348923</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>1.28514251661013</v>
+        <v>1.28677439767439</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0280538192757856</v>
+        <v>0.0281743852971031</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>1.25345259694664</v>
+        <v>1.26113808801741</v>
       </c>
       <c r="D18" t="n">
-        <v>0.12983801045033</v>
+        <v>0.131020992824456</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C19" t="n">
-        <v>1.21019935245141</v>
+        <v>1.22142748528159</v>
       </c>
       <c r="D19" t="n">
-        <v>0.338984282207476</v>
+        <v>0.34212872231661</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B20" t="s">
         <v>45</v>
       </c>
       <c r="C20" t="n">
-        <v>1.19723506491294</v>
+        <v>1.20921196029538</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0749036926377224</v>
+        <v>0.0756545091627718</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>1.03581441499248</v>
+        <v>1.04484507768321</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0588392171228113</v>
+        <v>0.0594324548923331</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
       </c>
       <c r="C22" t="n">
-        <v>0.913580062960667</v>
+        <v>0.923176232746477</v>
       </c>
       <c r="D22" t="n">
-        <v>0.093826376811375</v>
+        <v>0.0948126436621205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
       </c>
       <c r="C23" t="n">
-        <v>0.795096936038915</v>
+        <v>0.793776359996363</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0343760204380203</v>
+        <v>0.0339340415734065</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>0.770776594441948</v>
+        <v>0.779268976174299</v>
       </c>
       <c r="D24" t="n">
-        <v>0.124140389772363</v>
+        <v>0.125551316398741</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B25" t="s">
         <v>56</v>
       </c>
       <c r="C25" t="n">
-        <v>0.740709254180603</v>
+        <v>0.724432320623342</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0343030867573861</v>
+        <v>0.0329106405924696</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
       </c>
       <c r="C26" t="n">
-        <v>0.68586630615025</v>
+        <v>0.683603758773122</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0994719985593167</v>
+        <v>0.0983935336643668</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s">
-        <v>227</v>
+        <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>0.634414422737316</v>
+        <v>0.617899697480469</v>
       </c>
       <c r="D27" t="n">
-        <v>0.361269343806202</v>
+        <v>0.0231710099600266</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C28" t="n">
-        <v>0.611937454293534</v>
+        <v>0.601389586050075</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0229257232687582</v>
+        <v>0.0540686783394742</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>253</v>
       </c>
       <c r="C29" t="n">
-        <v>0.59479154173806</v>
+        <v>0.581165372990143</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0534758047290693</v>
+        <v>0.287717329146073</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="C30" t="n">
-        <v>0.575801255151112</v>
+        <v>0.563390110406617</v>
       </c>
       <c r="D30" t="n">
-        <v>0.285076407575839</v>
+        <v>0.0685115467636428</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.558052680413921</v>
+        <v>0.54571878241808</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0678834815202903</v>
+        <v>0.0248336220151589</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>0.539940742373557</v>
+        <v>0.537452727145315</v>
       </c>
       <c r="D32" t="n">
-        <v>0.024583978825797</v>
+        <v>0.0130265086890308</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C33" t="n">
-        <v>0.53231820900024</v>
+        <v>0.536991755890864</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0128969765074405</v>
+        <v>0.013475418109048</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C34" t="n">
-        <v>0.53133730379142</v>
+        <v>0.535897075431976</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0133372182812569</v>
+        <v>0.139977746502613</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C35" t="n">
-        <v>0.530249905132421</v>
+        <v>0.513947278718301</v>
       </c>
       <c r="D35" t="n">
-        <v>0.138525410573065</v>
+        <v>0.0793479837468379</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C36" t="n">
-        <v>0.508663718367773</v>
+        <v>0.50809659159924</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0785202334983789</v>
+        <v>0.0160226440917826</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C37" t="n">
-        <v>0.503053751062325</v>
+        <v>0.507431702016306</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0158691435437323</v>
+        <v>0.0619300384488777</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" t="n">
-        <v>0.502394483652806</v>
+        <v>0.487139022322525</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0613094177263046</v>
+        <v>0.0206026307974216</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="C39" t="n">
-        <v>0.483640315375613</v>
+        <v>0.483510492761259</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0204284593476834</v>
+        <v>0.0563888807995842</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="C40" t="n">
-        <v>0.480397425228766</v>
+        <v>0.464393441290844</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0559039825327892</v>
+        <v>0.197096879580637</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="C41" t="n">
-        <v>0.469645145438981</v>
+        <v>0.447274807398038</v>
       </c>
       <c r="D41" t="n">
-        <v>0.199267878802988</v>
+        <v>0.0484745640733263</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C42" t="n">
-        <v>0.442773364902181</v>
+        <v>0.437249810629596</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0480059618920519</v>
+        <v>0.172544225154919</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="C43" t="n">
-        <v>0.433138109768814</v>
+        <v>0.4292005813294</v>
       </c>
       <c r="D43" t="n">
-        <v>0.170918567060812</v>
+        <v>0.0310287177155646</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C44" t="n">
-        <v>0.424831865313933</v>
+        <v>0.419467342213458</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0307084493930197</v>
+        <v>0.0585565269261787</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C45" t="n">
-        <v>0.415651342550851</v>
+        <v>0.410306282123798</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0580065619102386</v>
+        <v>0.0393649768748636</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="C46" t="n">
-        <v>0.40580020909095</v>
+        <v>0.374891186203305</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0389056366961659</v>
+        <v>0.0603501710173934</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C47" t="n">
-        <v>0.37088930739431</v>
+        <v>0.335688673234865</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0596733269801258</v>
+        <v>0.0110135850242286</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="C48" t="n">
-        <v>0.332414100168921</v>
+        <v>0.325872129306395</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0109103823430571</v>
+        <v>0.0111491770541813</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="C49" t="n">
-        <v>0.322559052162815</v>
+        <v>0.314669483987686</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0110423899584782</v>
+        <v>0.0223099636957097</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="C50" t="n">
-        <v>0.311623189052691</v>
+        <v>0.299829666598193</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0220995333354377</v>
+        <v>0.0126450923366812</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C51" t="n">
-        <v>0.29675247302869</v>
+        <v>0.282748386304968</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0125182079658707</v>
+        <v>0.0236056310039356</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C52" t="n">
-        <v>0.279716768293944</v>
+        <v>0.281089922400473</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0233561622196289</v>
+        <v>0.0203196095686325</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="C53" t="n">
-        <v>0.278398767276661</v>
+        <v>0.265971726412176</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0201377523374309</v>
+        <v>0.0377133349732181</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B54" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C54" t="n">
-        <v>0.267712167344517</v>
+        <v>0.244899425015592</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0379547208933267</v>
+        <v>0.0548530700737749</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B55" t="s">
-        <v>216</v>
+        <v>42</v>
       </c>
       <c r="C55" t="n">
-        <v>0.244937938048259</v>
+        <v>0.227840884624036</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0541743567036362</v>
+        <v>0.0119610030956442</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>265</v>
       </c>
       <c r="C56" t="n">
-        <v>0.22562721471596</v>
+        <v>0.211319234882233</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0118222468732279</v>
+        <v>0.0248521060651113</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>283</v>
+      </c>
+      <c r="B57" t="s">
         <v>284</v>
       </c>
-      <c r="B57" t="s">
-        <v>285</v>
-      </c>
       <c r="C57" t="n">
-        <v>0.208176946193014</v>
+        <v>0.210108206041956</v>
       </c>
       <c r="D57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B58" t="s">
-        <v>266</v>
+        <v>14</v>
       </c>
       <c r="C58" t="n">
-        <v>0.208128592650681</v>
+        <v>0.198817317333851</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0244033764142258</v>
+        <v>0.0245496145099212</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="C59" t="n">
-        <v>0.196629635413949</v>
+        <v>0.196711440813216</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0242739525489436</v>
+        <v>0.0925166929574372</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C60" t="n">
-        <v>0.194899228057228</v>
+        <v>0.195970272665752</v>
       </c>
       <c r="D60" t="n">
-        <v>0.091666968535913</v>
+        <v>0.107557432972455</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="C61" t="n">
-        <v>0.193949528009353</v>
+        <v>0.178755381420178</v>
       </c>
       <c r="D61" t="n">
-        <v>0.106489376473915</v>
+        <v>0.0157908560339566</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="C62" t="n">
-        <v>0.176944383425097</v>
+        <v>0.17699051363226</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0156345547592388</v>
+        <v>0.124462169083388</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B63" t="s">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="C63" t="n">
-        <v>0.175363662977254</v>
+        <v>0.175951998261204</v>
       </c>
       <c r="D63" t="n">
-        <v>0.123318145275889</v>
+        <v>0.06952476620221</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B64" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="C64" t="n">
-        <v>0.173458613479594</v>
+        <v>0.175175541737212</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0684884422434154</v>
+        <v>0.0523071196786227</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B65" t="s">
-        <v>267</v>
+        <v>87</v>
       </c>
       <c r="C65" t="n">
-        <v>0.173404832952749</v>
+        <v>0.17175429771593</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0517786047873365</v>
+        <v>0.0182171186806901</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="C66" t="n">
-        <v>0.170078113688582</v>
+        <v>0.161199638578423</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0180427694811143</v>
+        <v>0.0596401150241016</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B67" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="C67" t="n">
-        <v>0.159653343517406</v>
+        <v>0.157356842125326</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0590639015250098</v>
+        <v>0.0878773921080886</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B68" t="s">
         <v>58</v>
       </c>
       <c r="C68" t="n">
-        <v>0.156631291605068</v>
+        <v>0.155081482625821</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00988841897842502</v>
+        <v>0.00957300588467285</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="C69" t="n">
-        <v>0.155770892142505</v>
+        <v>0.154372347883767</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0869917530196702</v>
+        <v>0.0680309953370037</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s">
-        <v>253</v>
+        <v>41</v>
       </c>
       <c r="C70" t="n">
-        <v>0.15278940916357</v>
+        <v>0.135186403266047</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0673297669470753</v>
+        <v>0.0180867254134663</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C71" t="n">
-        <v>0.133696565914387</v>
+        <v>0.125973286086585</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0178803621938935</v>
+        <v>0.0115527892054083</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="C72" t="n">
-        <v>0.12480540818615</v>
+        <v>0.12343894312652</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0114460781195679</v>
+        <v>0.0356384020393722</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B73" t="s">
-        <v>205</v>
+        <v>63</v>
       </c>
       <c r="C73" t="n">
-        <v>0.12454042009813</v>
-      </c>
-      <c r="D73"/>
+        <v>0.118412818759759</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.0142787856552056</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B74" t="s">
-        <v>259</v>
+        <v>120</v>
       </c>
       <c r="C74" t="n">
-        <v>0.122253346477603</v>
+        <v>0.11818721558921</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0353025553632196</v>
+        <v>0.0359403375213512</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B75" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="C75" t="n">
-        <v>0.121468435479933</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.0370623980907105</v>
-      </c>
+        <v>0.117418436307439</v>
+      </c>
+      <c r="D75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B76" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C76" t="n">
-        <v>0.116906899305349</v>
+        <v>0.112114202718795</v>
       </c>
       <c r="D76" t="n">
-        <v>0.014079118323508</v>
+        <v>0.0338127557868243</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>235</v>
       </c>
       <c r="C77" t="n">
-        <v>0.110829143728351</v>
+        <v>0.11155802917118</v>
       </c>
       <c r="D77" t="n">
-        <v>0.033402721248871</v>
+        <v>0.0317103665692805</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B78" t="s">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="C78" t="n">
-        <v>0.110420006924664</v>
+        <v>0.108794356659839</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0313909523245771</v>
+        <v>0.0290445478347597</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C79" t="n">
-        <v>0.107639211163976</v>
+        <v>0.104449508971983</v>
       </c>
       <c r="D79" t="n">
-        <v>0.028744368517691</v>
+        <v>0.00836673921016216</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="C80" t="n">
-        <v>0.103429428104386</v>
+        <v>0.104448004950846</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00828772946842191</v>
+        <v>0.0280579854032269</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B81" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="C81" t="n">
-        <v>0.103395620659884</v>
+        <v>0.102106311384776</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0277755264151185</v>
+        <v>0.0158547105903662</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.101126518365119</v>
+        <v>0.100003263321802</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0157067411332251</v>
+        <v>0.0122719910044211</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B83" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0990262976006827</v>
+        <v>0.099773327672455</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0121570348357733</v>
+        <v>0.00629639076465932</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0987132006294671</v>
+        <v>0.0968919149989711</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00622806908915873</v>
+        <v>0.0103001376237518</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B85" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0956144369565472</v>
+        <v>0.0944420890475745</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0101316806639784</v>
+        <v>0.0372485283916166</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0935175524530813</v>
+        <v>0.0926996468882519</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0368839010250521</v>
+        <v>0.0133129174339312</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B87" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0917329197347184</v>
+        <v>0.09001137746645</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0131688102035404</v>
+        <v>0.019300954403762</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0890420250863173</v>
+        <v>0.0818029015103466</v>
       </c>
       <c r="D88" t="n">
-        <v>0.019072714477922</v>
+        <v>0.039824487345065</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B89" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0810488108774321</v>
+        <v>0.0808196308559792</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0394587927912284</v>
+        <v>0.0452965340806616</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C90" t="n">
-        <v>0.079910122766446</v>
+        <v>0.0795922373678087</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0447853982793154</v>
+        <v>0.0352438227503994</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>61</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0786202353082748</v>
+        <v>0.0762795297972343</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0348025089453629</v>
+        <v>0.00179389654034583</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B92" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0758282964359459</v>
+        <v>0.0748840675590239</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00179354153556445</v>
+        <v>0.0193295447582689</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B93" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0741341653568439</v>
+        <v>0.0747947017657944</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0191477054435941</v>
+        <v>0.00612372977989521</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>278</v>
       </c>
       <c r="C94" t="n">
-        <v>0.074039126402663</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.00606339646283336</v>
-      </c>
+        <v>0.0746371162675601</v>
+      </c>
+      <c r="D94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B95" t="s">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0739510713547805</v>
-      </c>
-      <c r="D95"/>
+        <v>0.0738608168801044</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.00799110880951997</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B96" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0730662949453925</v>
+        <v>0.0718269762375084</v>
       </c>
       <c r="D96" t="n">
-        <v>0.00790033664291753</v>
+        <v>0.00793661066492192</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B97" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="C97" t="n">
-        <v>0.071126792992777</v>
+        <v>0.0696937804075641</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00786309949772369</v>
+        <v>0.00619216063132812</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B98" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0711195866690807</v>
+        <v>0.0694585919082762</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00656720286960041</v>
+        <v>0.00500934688503574</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0687520201922047</v>
+        <v>0.0690987941353845</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00495698776500924</v>
+        <v>0.00207850006255702</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B100" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0683910589969318</v>
+        <v>0.067029305947034</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00205836273212492</v>
+        <v>0.00347566673017067</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="C101" t="n">
-        <v>0.067587798563924</v>
+        <v>0.0638769674362012</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00361265724822627</v>
+        <v>0.0134806353744407</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B102" t="s">
         <v>222</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0656049474604313</v>
+        <v>0.0629046289951729</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0211011863531491</v>
+        <v>0.0198245944490694</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B103" t="s">
-        <v>221</v>
+        <v>116</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0632680745844844</v>
+        <v>0.0623758869972511</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0133574924839609</v>
+        <v>0.032091917340915</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B104" t="s">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0621565881212781</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0.0255910230939168</v>
-      </c>
+        <v>0.0622869477174784</v>
+      </c>
+      <c r="D104"/>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0617990743956747</v>
+        <v>0.0619268805676667</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0317962454449717</v>
+        <v>0.0253627720408859</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B106" t="s">
         <v>287</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0616720518196562</v>
+        <v>0.0610264433162174</v>
       </c>
       <c r="D106"/>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B107" t="s">
         <v>99</v>
       </c>
       <c r="C107" t="n">
-        <v>0.060472888418144</v>
+        <v>0.0602910892206106</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0185024096202656</v>
+        <v>0.0186711343081857</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B108" t="s">
-        <v>288</v>
+        <v>68</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0604515141061928</v>
-      </c>
-      <c r="D108"/>
+        <v>0.0582793150373827</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.00153884735296577</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B109" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0577043700978283</v>
+        <v>0.0566459031864538</v>
       </c>
       <c r="D109" t="n">
-        <v>0.00152347638934554</v>
+        <v>0.00465759501882641</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B110" t="s">
-        <v>94</v>
+        <v>288</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0560164222223917</v>
+        <v>0.0542827492590861</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00460561235237978</v>
+        <v>0.0281609770856999</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B111" t="s">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0533832448887809</v>
+        <v>0.0533696063962407</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0276755548138828</v>
+        <v>0.00540637165680088</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B112" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0528831838527762</v>
+        <v>0.0508836390414029</v>
       </c>
       <c r="D112" t="n">
-        <v>0.0166165255779122</v>
+        <v>0.0155996155026297</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B113" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0527591416698914</v>
+        <v>0.0504566317269566</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00534601674185898</v>
+        <v>0.00881430475350942</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B114" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0499271676659158</v>
+        <v>0.0488006595589728</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00871910088076297</v>
+        <v>0.00713049837984519</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B115" t="s">
-        <v>155</v>
+        <v>39</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0482915546042372</v>
+        <v>0.0473806391248837</v>
       </c>
       <c r="D115" t="n">
-        <v>0.00706137599549996</v>
+        <v>0.0153517835288353</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B116" t="s">
-        <v>39</v>
+        <v>290</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0469127446703312</v>
+        <v>0.045564455033695</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0151960570885899</v>
+        <v>0.0187301115991919</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B117" t="s">
         <v>47</v>
       </c>
       <c r="C117" t="n">
-        <v>0.045370413465389</v>
+        <v>0.0453505024149384</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00247003681816374</v>
+        <v>0.00244234498401862</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B118" t="s">
         <v>291</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0451368974391908</v>
+        <v>0.0437035992699299</v>
       </c>
       <c r="D118" t="n">
-        <v>0.0185550057139426</v>
+        <v>0.0222554464346034</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B119" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0437813523651193</v>
+        <v>0.043656503205073</v>
       </c>
       <c r="D119" t="n">
-        <v>0.00795095344513261</v>
+        <v>0.0066404939492731</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B120" t="s">
-        <v>292</v>
+        <v>95</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0432833375691765</v>
+        <v>0.0436387467764258</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0220403411555036</v>
+        <v>0.00281985356687905</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B121" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0432015324501788</v>
+        <v>0.0432826304881083</v>
       </c>
       <c r="D121" t="n">
-        <v>0.00657125099364605</v>
+        <v>0.0140210130386968</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B122" t="s">
-        <v>95</v>
+        <v>165</v>
       </c>
       <c r="C122" t="n">
-        <v>0.043075332818533</v>
+        <v>0.0432651434363811</v>
       </c>
       <c r="D122" t="n">
-        <v>0.00277818513479667</v>
+        <v>0.00638709212430936</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B123" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0428041170433677</v>
+        <v>0.0427733060765074</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0138642850309527</v>
+        <v>0.0183889114485384</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B124" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0428040503181483</v>
+        <v>0.0423879399442869</v>
       </c>
       <c r="D124" t="n">
-        <v>0.00632149963574228</v>
+        <v>0.00746650017863547</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B125" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0422267214780657</v>
+        <v>0.0371641827105098</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0181527903922321</v>
+        <v>0.00217478038726918</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B126" t="s">
-        <v>62</v>
+        <v>292</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0367734249877948</v>
-      </c>
-      <c r="D126" t="n">
-        <v>0.00215231362767521</v>
-      </c>
+        <v>0.0360355383116174</v>
+      </c>
+      <c r="D126"/>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B127" t="s">
-        <v>293</v>
+        <v>143</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0356129622135409</v>
-      </c>
-      <c r="D127"/>
+        <v>0.0351809849288848</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.00572464456305075</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B128" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0348454664981374</v>
+        <v>0.0344875189443471</v>
       </c>
       <c r="D128" t="n">
-        <v>0.00567197895517566</v>
+        <v>0.0175428090249012</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B129" t="s">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0341374451949687</v>
+        <v>0.0331912996531016</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0173662691263207</v>
+        <v>0.0199602948552977</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>293</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0336463698218446</v>
-      </c>
-      <c r="D130" t="n">
-        <v>0.00677129343649764</v>
-      </c>
+        <v>0.0330530643969582</v>
+      </c>
+      <c r="D130"/>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B131" t="s">
-        <v>244</v>
+        <v>168</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0328862138805763</v>
+        <v>0.0329089701928035</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0197768250291864</v>
+        <v>0.00797239973445631</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B132" t="s">
-        <v>294</v>
+        <v>142</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0326766744498864</v>
-      </c>
-      <c r="D132"/>
+        <v>0.0327804774019355</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.018549692324925</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B133" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0324612854416281</v>
+        <v>0.032736501619736</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0183800691174522</v>
+        <v>0.00639519463958896</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B134" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0323776342582267</v>
+        <v>0.0316862683526574</v>
       </c>
       <c r="D134" t="n">
-        <v>0.00782810812681507</v>
+        <v>0.00688915373999488</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B135" t="s">
-        <v>247</v>
+        <v>156</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0313923474266661</v>
+        <v>0.0311903454428294</v>
       </c>
       <c r="D135" t="n">
-        <v>0.00682394316080411</v>
+        <v>0.00419345281281257</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0308869483731085</v>
+        <v>0.0310348925118789</v>
       </c>
       <c r="D136" t="n">
-        <v>0.00415267304237246</v>
+        <v>0.0214365647612784</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B137" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="C137" t="n">
-        <v>0.030725606792573</v>
+        <v>0.0309017529691399</v>
       </c>
       <c r="D137" t="n">
-        <v>0.021223011797803</v>
+        <v>0.0065663146704989</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B138" t="s">
-        <v>174</v>
+        <v>257</v>
       </c>
       <c r="C138" t="n">
-        <v>0.030599896479203</v>
-      </c>
-      <c r="D138" t="n">
-        <v>0.0065017940110732</v>
-      </c>
+        <v>0.0307913757761459</v>
+      </c>
+      <c r="D138"/>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B139" t="s">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="C139" t="n">
-        <v>0.030482104225203</v>
-      </c>
-      <c r="D139"/>
+        <v>0.0293390974558798</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.00334435971516668</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B140" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0289476688378911</v>
+        <v>0.0292124903034522</v>
       </c>
       <c r="D140" t="n">
-        <v>0.00330079279408344</v>
+        <v>0.00364014967202993</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B141" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0289131496577158</v>
+        <v>0.0285636510953376</v>
       </c>
       <c r="D141" t="n">
-        <v>0.00360430450124728</v>
+        <v>0.000961156366460459</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B142" t="s">
-        <v>204</v>
+        <v>294</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0283489656858572</v>
-      </c>
-      <c r="D142" t="n">
-        <v>0.00377966048346676</v>
-      </c>
+        <v>0.028340000907459</v>
+      </c>
+      <c r="D142"/>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B143" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0282764353723576</v>
+        <v>0.0282708608313106</v>
       </c>
       <c r="D143" t="n">
-        <v>0.000951651091289559</v>
+        <v>0.00379116431205063</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
+        <v>151</v>
       </c>
       <c r="C144" t="n">
-        <v>0.028073323804471</v>
+        <v>0.0275517815912907</v>
       </c>
       <c r="D144"/>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0272888576415973</v>
-      </c>
-      <c r="D145"/>
+        <v>0.0272895431596136</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.00568488609869415</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0270327884912382</v>
+        <v>0.0249634061106773</v>
       </c>
       <c r="D146" t="n">
-        <v>0.00563254898061451</v>
+        <v>0.00429192290938485</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B147" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0247045009268554</v>
+        <v>0.0248032839797791</v>
       </c>
       <c r="D147" t="n">
-        <v>0.00424447822684661</v>
+        <v>0.0147720007475288</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B148" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0245361531982818</v>
+        <v>0.0224664616463471</v>
       </c>
       <c r="D148" t="n">
-        <v>0.0146131641682556</v>
+        <v>0.00270135199027758</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B149" t="s">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0231668849707516</v>
+        <v>0.0224333956294099</v>
       </c>
       <c r="D149" t="n">
-        <v>0.0158493759542961</v>
+        <v>0.00474308179233426</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B150" t="s">
-        <v>108</v>
+        <v>220</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0222404497827114</v>
+        <v>0.0222591985544386</v>
       </c>
       <c r="D150" t="n">
-        <v>0.00267571236202619</v>
+        <v>0.0152016879260899</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B151" t="s">
-        <v>88</v>
+        <v>295</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0222235238187209</v>
+        <v>0.0219875319305595</v>
       </c>
       <c r="D151" t="n">
-        <v>0.00469983563874982</v>
+        <v>0.00555494726406945</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B152" t="s">
-        <v>296</v>
+        <v>217</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0217092503109815</v>
+        <v>0.0209722503188585</v>
       </c>
       <c r="D152" t="n">
-        <v>0.00549269515823987</v>
+        <v>0.0066559571778465</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B153" t="s">
-        <v>217</v>
+        <v>76</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0207746746461732</v>
+        <v>0.020570205265671</v>
       </c>
       <c r="D153" t="n">
-        <v>0.00659445051451603</v>
+        <v>0.00270189861788245</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B154" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C154" t="n">
-        <v>0.020339559490395</v>
+        <v>0.0203050934801799</v>
       </c>
       <c r="D154" t="n">
-        <v>0.00267023546711689</v>
+        <v>0.00705913689371762</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B155" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0201036858397776</v>
+        <v>0.0200344594678277</v>
       </c>
       <c r="D155" t="n">
-        <v>0.00699142257046306</v>
+        <v>0.0137023701522382</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B156" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0198489734355466</v>
+        <v>0.019957485012921</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0135773651754865</v>
+        <v>0.00335275960580838</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B157" t="s">
-        <v>208</v>
+        <v>48</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0197389435487381</v>
+        <v>0.0194053745671841</v>
       </c>
       <c r="D157" t="n">
-        <v>0.00331393918521997</v>
+        <v>0.000908807680103533</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B158" t="s">
-        <v>48</v>
+        <v>296</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0192069211326355</v>
+        <v>0.0175817377145405</v>
       </c>
       <c r="D158" t="n">
-        <v>0.000899553026304408</v>
+        <v>0.00509102921011993</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B159" t="s">
         <v>297</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0174028491336842</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0.00503606749915178</v>
-      </c>
+        <v>0.0172797886352314</v>
+      </c>
+      <c r="D159"/>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B160" t="s">
-        <v>298</v>
+        <v>170</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0171098142117716</v>
-      </c>
-      <c r="D160"/>
+        <v>0.0162229331855347</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.00392285435021007</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B161" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0160695457994164</v>
+        <v>0.0150600105735649</v>
       </c>
       <c r="D161" t="n">
-        <v>0.00388712421060206</v>
+        <v>0.0045906267837283</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B162" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0149075928285957</v>
+        <v>0.0149867624993856</v>
       </c>
       <c r="D162" t="n">
-        <v>0.00454550594379647</v>
+        <v>0.0100804739075933</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B163" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0148201827911675</v>
+        <v>0.0138901739539802</v>
       </c>
       <c r="D163" t="n">
-        <v>0.00996743425827934</v>
+        <v>0.00772333734896872</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B164" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0137461736595303</v>
+        <v>0.0138127056413867</v>
       </c>
       <c r="D164" t="n">
-        <v>0.00764482880349439</v>
+        <v>0.00256601054780082</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0136633899039812</v>
+        <v>0.0136648401603512</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00253793496436115</v>
+        <v>0.00307600468567943</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0135624346470126</v>
+        <v>0.0133690643021268</v>
       </c>
       <c r="D166" t="n">
-        <v>0.00336706196956387</v>
+        <v>0.00639011660638637</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B167" t="s">
-        <v>134</v>
+        <v>298</v>
       </c>
       <c r="C167" t="n">
-        <v>0.013509388097581</v>
+        <v>0.0133114625373876</v>
       </c>
       <c r="D167" t="n">
-        <v>0.0030382550755874</v>
+        <v>0.00469778598241589</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B168" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0132314108335153</v>
+        <v>0.0132020281636138</v>
       </c>
       <c r="D168" t="n">
-        <v>0.0063332990493948</v>
+        <v>0.00359078577135605</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B169" t="s">
-        <v>299</v>
+        <v>169</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0130938234310901</v>
+        <v>0.01307755357847</v>
       </c>
       <c r="D169" t="n">
-        <v>0.00461036727470488</v>
+        <v>0.00315570615180139</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B170" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0130581921639247</v>
+        <v>0.0128858470036949</v>
       </c>
       <c r="D170" t="n">
-        <v>0.00355034122475857</v>
+        <v>0.00547909634990868</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B171" t="s">
-        <v>125</v>
+        <v>299</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0127508780450581</v>
-      </c>
-      <c r="D171" t="n">
-        <v>0.00542071033253353</v>
-      </c>
+        <v>0.0127907793989909</v>
+      </c>
+      <c r="D171"/>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B172" t="s">
-        <v>300</v>
+        <v>172</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0126546825204074</v>
-      </c>
-      <c r="D172"/>
+        <v>0.0124968442830536</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.0032935237028684</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="C173" t="n">
-        <v>0.012375437477173</v>
+        <v>0.0118132779003281</v>
       </c>
       <c r="D173" t="n">
-        <v>0.00326058756429147</v>
+        <v>0.00612462167662601</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B174" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0116857433676025</v>
+        <v>0.0117953194389909</v>
       </c>
       <c r="D174" t="n">
-        <v>0.00605866919801713</v>
+        <v>0.00127486409332423</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B175" t="s">
-        <v>113</v>
+        <v>300</v>
       </c>
       <c r="C175" t="n">
-        <v>0.011682518315331</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0.00126266954612942</v>
-      </c>
+        <v>0.0112512678527791</v>
+      </c>
+      <c r="D175"/>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B176" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0113871702524787</v>
+        <v>0.0111097776255183</v>
       </c>
       <c r="D176" t="n">
-        <v>0.000850884833701265</v>
+        <v>0.0038724545052133</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B177" t="s">
-        <v>301</v>
+        <v>100</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0110495851257394</v>
-      </c>
-      <c r="D177"/>
+        <v>0.0110308277398645</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.00162226739298024</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B178" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="C178" t="n">
-        <v>0.0109911560752753</v>
+        <v>0.010892255762571</v>
       </c>
       <c r="D178" t="n">
-        <v>0.0038344064565906</v>
+        <v>0.00131159361871773</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B179" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0109140439633761</v>
+        <v>0.0108152139634342</v>
       </c>
       <c r="D179" t="n">
-        <v>0.00160511214397644</v>
+        <v>0.00327309169461479</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B180" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C180" t="n">
-        <v>0.0107730980582406</v>
+        <v>0.0103933697066224</v>
       </c>
       <c r="D180" t="n">
-        <v>0.00129888789638912</v>
+        <v>0.000223780193696136</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B181" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0107139572721028</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0.00324240042163417</v>
-      </c>
+        <v>0.0100941368445906</v>
+      </c>
+      <c r="D181"/>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B182" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0102790645337226</v>
+        <v>0.00986803981635471</v>
       </c>
       <c r="D182" t="n">
-        <v>0.00023156854493671</v>
+        <v>0.000901306620846263</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B183" t="s">
-        <v>145</v>
+        <v>301</v>
       </c>
       <c r="C183" t="n">
-        <v>0.00998683031444283</v>
+        <v>0.00980065069018671</v>
       </c>
       <c r="D183"/>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B184" t="s">
-        <v>302</v>
+        <v>110</v>
       </c>
       <c r="C184" t="n">
-        <v>0.00971056566434207</v>
-      </c>
-      <c r="D184"/>
+        <v>0.00968295542419775</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.00109529121465298</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B185" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0095866569318961</v>
+        <v>0.00958337575608274</v>
       </c>
       <c r="D185" t="n">
-        <v>0.00108480281586065</v>
+        <v>0.00204779771115841</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B186" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C186" t="n">
-        <v>0.00949319714124129</v>
+        <v>0.00958265741762925</v>
       </c>
       <c r="D186"/>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B187" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C187" t="n">
-        <v>0.00947673825378661</v>
+        <v>0.00875701715764953</v>
       </c>
       <c r="D187" t="n">
-        <v>0.00202426348645485</v>
+        <v>0.00275458686695689</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B188" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="C188" t="n">
-        <v>0.00867438973211082</v>
+        <v>0.00854699295231048</v>
       </c>
       <c r="D188" t="n">
-        <v>0.00272855950202667</v>
+        <v>0.00240399051976314</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B189" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="C189" t="n">
-        <v>0.00851525008381592</v>
-      </c>
-      <c r="D189" t="n">
-        <v>0.00237787038648958</v>
-      </c>
+        <v>0.00852916917943327</v>
+      </c>
+      <c r="D189"/>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B190" t="s">
-        <v>303</v>
+        <v>102</v>
       </c>
       <c r="C190" t="n">
-        <v>0.00837630593526271</v>
-      </c>
-      <c r="D190"/>
+        <v>0.00823359535389893</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.000768431047204379</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B191" t="s">
-        <v>102</v>
+        <v>268</v>
       </c>
       <c r="C191" t="n">
-        <v>0.00814425786389154</v>
-      </c>
-      <c r="D191" t="n">
-        <v>0.000760375394741629</v>
-      </c>
+        <v>0.00801046147178369</v>
+      </c>
+      <c r="D191"/>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B192" t="s">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="C192" t="n">
-        <v>0.007935697069753</v>
-      </c>
-      <c r="D192"/>
+        <v>0.00755947961145219</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.00155775558942273</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B193" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="C193" t="n">
-        <v>0.00748705893617418</v>
+        <v>0.00748279698154216</v>
       </c>
       <c r="D193" t="n">
-        <v>0.00154249887950655</v>
+        <v>0.00169327944661371</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B194" t="s">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="C194" t="n">
-        <v>0.00740147272140985</v>
+        <v>0.00715195722755681</v>
       </c>
       <c r="D194" t="n">
-        <v>0.00167481812015553</v>
+        <v>0.00262226374503717</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B195" t="s">
         <v>304</v>
       </c>
       <c r="C195" t="n">
-        <v>0.00707876731859912</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.0025948448933685</v>
-      </c>
+        <v>0.00712587256246447</v>
+      </c>
+      <c r="D195"/>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B196" t="s">
-        <v>305</v>
+        <v>64</v>
       </c>
       <c r="C196" t="n">
-        <v>0.00705941700496997</v>
-      </c>
-      <c r="D196"/>
+        <v>0.00701747080021754</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.00132051999106952</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B197" t="s">
-        <v>64</v>
+        <v>210</v>
       </c>
       <c r="C197" t="n">
-        <v>0.006937888138683</v>
-      </c>
-      <c r="D197" t="n">
-        <v>0.00130603710284864</v>
-      </c>
+        <v>0.00684935715402428</v>
+      </c>
+      <c r="D197"/>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B198" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C198" t="n">
-        <v>0.00677538998767775</v>
+        <v>0.0066957000692075</v>
       </c>
       <c r="D198"/>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B199" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C199" t="n">
-        <v>0.00662187749955316</v>
-      </c>
-      <c r="D199"/>
+        <v>0.00658458208968331</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.00276122028616907</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B200" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C200" t="n">
-        <v>0.00652350228440175</v>
+        <v>0.00653474735947246</v>
       </c>
       <c r="D200" t="n">
-        <v>0.00273544668709877</v>
+        <v>0.00303736551909417</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B201" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="C201" t="n">
-        <v>0.00646620756266763</v>
+        <v>0.00649425102915698</v>
       </c>
       <c r="D201" t="n">
-        <v>0.00300571182071141</v>
+        <v>0.00093680513191265</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B202" t="s">
-        <v>54</v>
+        <v>305</v>
       </c>
       <c r="C202" t="n">
-        <v>0.00642572759622504</v>
+        <v>0.00609530381055014</v>
       </c>
       <c r="D202" t="n">
-        <v>0.000926806877616954</v>
+        <v>0.00100904263959922</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B203" t="s">
         <v>306</v>
       </c>
       <c r="C203" t="n">
-        <v>0.00603636369922286</v>
-      </c>
-      <c r="D203" t="n">
-        <v>0.000997707508400918</v>
-      </c>
+        <v>0.0054828978308735</v>
+      </c>
+      <c r="D203"/>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B204" t="s">
         <v>307</v>
       </c>
       <c r="C204" t="n">
-        <v>0.00542925316954325</v>
+        <v>0.00538378957236859</v>
       </c>
       <c r="D204"/>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B205" t="s">
         <v>308</v>
       </c>
       <c r="C205" t="n">
-        <v>0.00532000174362787</v>
+        <v>0.00535651515921266</v>
       </c>
       <c r="D205"/>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B206" t="s">
-        <v>309</v>
+        <v>146</v>
       </c>
       <c r="C206" t="n">
-        <v>0.00530327595529555</v>
-      </c>
-      <c r="D206"/>
+        <v>0.00529554618297272</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.0016137263583178</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B207" t="s">
-        <v>146</v>
+        <v>248</v>
       </c>
       <c r="C207" t="n">
-        <v>0.00523837455854859</v>
+        <v>0.00528744242729429</v>
       </c>
       <c r="D207" t="n">
-        <v>0.00159602646511648</v>
+        <v>0.000202780196637773</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B208" t="s">
-        <v>249</v>
+        <v>173</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00520325485139867</v>
+        <v>0.00516083527486673</v>
       </c>
       <c r="D208" t="n">
-        <v>0.000196491119433844</v>
+        <v>0.000150430195464483</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B209" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00510403445013472</v>
+        <v>0.00505618234142395</v>
       </c>
       <c r="D209" t="n">
-        <v>0.000147521933680138</v>
+        <v>0.00132409809090847</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B210" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C210" t="n">
-        <v>0.0050061930367386</v>
-      </c>
-      <c r="D210" t="n">
-        <v>0.00131184796425344</v>
-      </c>
+        <v>0.00499054416523633</v>
+      </c>
+      <c r="D210"/>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B211" t="s">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="C211" t="n">
-        <v>0.0049331066797439</v>
-      </c>
-      <c r="D211"/>
+        <v>0.00483803193232979</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.00131640713405925</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B212" t="s">
-        <v>66</v>
+        <v>309</v>
       </c>
       <c r="C212" t="n">
-        <v>0.00478671154835647</v>
-      </c>
-      <c r="D212" t="n">
-        <v>0.00130298323785388</v>
-      </c>
+        <v>0.004292274292291</v>
+      </c>
+      <c r="D212"/>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B213" t="s">
         <v>310</v>
       </c>
       <c r="C213" t="n">
-        <v>0.00424857265380789</v>
+        <v>0.00413143382293932</v>
       </c>
       <c r="D213"/>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B214" t="s">
         <v>311</v>
       </c>
       <c r="C214" t="n">
-        <v>0.00409345876041744</v>
-      </c>
-      <c r="D214"/>
+        <v>0.00386589552399151</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.000988899685485546</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B215" t="s">
-        <v>312</v>
+        <v>74</v>
       </c>
       <c r="C215" t="n">
-        <v>0.0038259351140595</v>
+        <v>0.00376225275399895</v>
       </c>
       <c r="D215" t="n">
-        <v>0.000979104747787664</v>
+        <v>0.000818511923715131</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B216" t="s">
-        <v>74</v>
+        <v>312</v>
       </c>
       <c r="C216" t="n">
-        <v>0.00372591401016262</v>
-      </c>
-      <c r="D216" t="n">
-        <v>0.000810880299450492</v>
-      </c>
+        <v>0.00375621422137431</v>
+      </c>
+      <c r="D216"/>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B217" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="C217" t="n">
-        <v>0.0037208651352272</v>
-      </c>
-      <c r="D217"/>
+        <v>0.00357368890995791</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.00142725875052934</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B218" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C218" t="n">
-        <v>0.00353966168104711</v>
+        <v>0.00349581653198429</v>
       </c>
       <c r="D218" t="n">
-        <v>0.00141412459338223</v>
+        <v>0.00227600869864577</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B219" t="s">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="C219" t="n">
-        <v>0.00346355044743912</v>
+        <v>0.00343190685770038</v>
       </c>
       <c r="D219" t="n">
-        <v>0.00225518258381621</v>
+        <v>0.000901455538727818</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B220" t="s">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="C220" t="n">
-        <v>0.00339684746976806</v>
-      </c>
-      <c r="D220" t="n">
-        <v>0.000892830758197395</v>
-      </c>
+        <v>0.0034234439327952</v>
+      </c>
+      <c r="D220"/>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B221" t="s">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="C221" t="n">
-        <v>0.00338623815988174</v>
-      </c>
-      <c r="D221"/>
+        <v>0.00337868246791213</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.000837387700776559</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B222" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C222" t="n">
-        <v>0.00334088725242216</v>
+        <v>0.00312800479572089</v>
       </c>
       <c r="D222" t="n">
-        <v>0.000827914908552231</v>
+        <v>0.000981804891480866</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B223" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C223" t="n">
-        <v>0.00313790913497432</v>
-      </c>
-      <c r="D223"/>
+        <v>0.00307960674241703</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.000774992493759413</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B224" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="C224" t="n">
-        <v>0.00309527171977078</v>
-      </c>
-      <c r="D224" t="n">
-        <v>0.000970494573507885</v>
-      </c>
+        <v>0.00301374408546269</v>
+      </c>
+      <c r="D224"/>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B225" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C225" t="n">
-        <v>0.00305085496538295</v>
-      </c>
-      <c r="D225" t="n">
-        <v>0.000767554419117853</v>
-      </c>
+        <v>0.00294907117657194</v>
+      </c>
+      <c r="D225"/>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B226" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="C226" t="n">
-        <v>0.00298366266943621</v>
+        <v>0.00292276203071288</v>
       </c>
       <c r="D226"/>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B227" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C227" t="n">
-        <v>0.00289120375707257</v>
-      </c>
-      <c r="D227"/>
+        <v>0.00271082973885675</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.000909473527360676</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B228" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="C228" t="n">
-        <v>0.00268242054553598</v>
+        <v>0.00255400747522928</v>
       </c>
       <c r="D228" t="n">
-        <v>0.000899653736424912</v>
+        <v>0.000499529202412927</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B229" t="s">
-        <v>73</v>
+        <v>315</v>
       </c>
       <c r="C229" t="n">
-        <v>0.00252626129037477</v>
-      </c>
-      <c r="D229" t="n">
-        <v>0.00049408838683318</v>
-      </c>
+        <v>0.002549652548355</v>
+      </c>
+      <c r="D229"/>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B230" t="s">
-        <v>316</v>
+        <v>171</v>
       </c>
       <c r="C230" t="n">
-        <v>0.00252528265382341</v>
-      </c>
-      <c r="D230"/>
+        <v>0.00252596982746651</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.00135034791161328</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B231" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0025012615748355</v>
-      </c>
-      <c r="D231" t="n">
-        <v>0.00133729104699597</v>
-      </c>
+        <v>0.00246140915895912</v>
+      </c>
+      <c r="D231"/>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B232" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="C232" t="n">
-        <v>0.00243671604592539</v>
+        <v>0.0024101377518413</v>
       </c>
       <c r="D232"/>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B233" t="s">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="C233" t="n">
-        <v>0.00238607160439255</v>
-      </c>
-      <c r="D233"/>
+        <v>0.002408790867241</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.000443342732240052</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B234" t="s">
-        <v>119</v>
+        <v>239</v>
       </c>
       <c r="C234" t="n">
-        <v>0.00238560452785668</v>
+        <v>0.00229982790307729</v>
       </c>
       <c r="D234" t="n">
-        <v>0.000439203678693502</v>
+        <v>0.000570434729809766</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B235" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="C235" t="n">
-        <v>0.00227408444448132</v>
-      </c>
-      <c r="D235" t="n">
-        <v>0.000565962079468385</v>
-      </c>
+        <v>0.0022747982975885</v>
+      </c>
+      <c r="D235"/>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B236" t="s">
-        <v>317</v>
+        <v>195</v>
       </c>
       <c r="C236" t="n">
-        <v>0.00225388894473964</v>
-      </c>
-      <c r="D236"/>
+        <v>0.00227428199182506</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.00107021790321852</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B237" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="C237" t="n">
-        <v>0.00225041923333027</v>
-      </c>
-      <c r="D237" t="n">
-        <v>0.00105920119290938</v>
-      </c>
+        <v>0.00217362481602981</v>
+      </c>
+      <c r="D237"/>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B238" t="s">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="C238" t="n">
-        <v>0.00214999777811693</v>
-      </c>
-      <c r="D238"/>
+        <v>0.00200447855830966</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.000133255183443219</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B239" t="s">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="C239" t="n">
-        <v>0.00198354059742664</v>
+        <v>0.00200369287562616</v>
       </c>
       <c r="D239" t="n">
-        <v>0.000132251780719164</v>
+        <v>0.00120425109626506</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B240" t="s">
-        <v>318</v>
+        <v>219</v>
       </c>
       <c r="C240" t="n">
-        <v>0.00198338490524801</v>
-      </c>
-      <c r="D240" t="n">
-        <v>0.00119184511494118</v>
-      </c>
+        <v>0.00191746981313072</v>
+      </c>
+      <c r="D240"/>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B241" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="C241" t="n">
-        <v>0.00189713143828957</v>
-      </c>
-      <c r="D241"/>
+        <v>0.00185382951576687</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.000779452859373586</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B242" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C242" t="n">
-        <v>0.00183569975295197</v>
+        <v>0.00182848563720469</v>
       </c>
       <c r="D242" t="n">
-        <v>0.000771517694948066</v>
+        <v>0.00108036086986427</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B243" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="C243" t="n">
-        <v>0.00181029968609624</v>
+        <v>0.001600256041685</v>
       </c>
       <c r="D243" t="n">
-        <v>0.0010694553827558</v>
+        <v>0.000442528587037495</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B244" t="s">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C244" t="n">
-        <v>0.00158503534536518</v>
+        <v>0.00159796633786451</v>
       </c>
       <c r="D244" t="n">
-        <v>0.000438099252088905</v>
+        <v>0.000561450505832463</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B245" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="C245" t="n">
-        <v>0.0015777845381892</v>
-      </c>
-      <c r="D245" t="n">
-        <v>0.000554544070528963</v>
-      </c>
+        <v>0.00149989069088649</v>
+      </c>
+      <c r="D245"/>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B246" t="s">
-        <v>278</v>
+        <v>107</v>
       </c>
       <c r="C246" t="n">
-        <v>0.00148436923101399</v>
+        <v>0.00126346754738169</v>
       </c>
       <c r="D246"/>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B247" t="s">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="C247" t="n">
-        <v>0.00127009230974592</v>
-      </c>
-      <c r="D247"/>
+        <v>0.00123459932078208</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.000447877851137056</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B248" t="s">
-        <v>107</v>
+        <v>318</v>
       </c>
       <c r="C248" t="n">
-        <v>0.00125149821527009</v>
-      </c>
-      <c r="D248"/>
+        <v>0.00122481195935328</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.000165271625532996</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B249" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="C249" t="n">
-        <v>0.00122325120571949</v>
-      </c>
-      <c r="D249" t="n">
-        <v>0.000443761074703495</v>
-      </c>
+        <v>0.00120595557494918</v>
+      </c>
+      <c r="D249"/>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B250" t="s">
-        <v>319</v>
+        <v>187</v>
       </c>
       <c r="C250" t="n">
-        <v>0.00121050668881202</v>
-      </c>
-      <c r="D250" t="n">
-        <v>0.000162352763473355</v>
-      </c>
+        <v>0.00119367647700984</v>
+      </c>
+      <c r="D250"/>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B251" t="s">
         <v>320</v>
       </c>
       <c r="C251" t="n">
-        <v>0.00119538230574556</v>
-      </c>
-      <c r="D251"/>
+        <v>0.00115930847162569</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.000169970088955755</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B252" t="s">
-        <v>321</v>
+        <v>213</v>
       </c>
       <c r="C252" t="n">
-        <v>0.00119031118907033</v>
+        <v>0.00112985659503261</v>
       </c>
       <c r="D252"/>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B253" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C253" t="n">
-        <v>0.00114504924856997</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.0001685021319242</v>
-      </c>
+        <v>0.00112345889318122</v>
+      </c>
+      <c r="D253"/>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B254" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="C254" t="n">
-        <v>0.00111844812776484</v>
+        <v>0.00111497352019937</v>
       </c>
       <c r="D254"/>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B255" t="s">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="C255" t="n">
-        <v>0.0011035016786168</v>
-      </c>
-      <c r="D255"/>
+        <v>0.00110752075874442</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.000597482640865109</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B256" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C256" t="n">
-        <v>0.00109311478612851</v>
-      </c>
-      <c r="D256" t="n">
-        <v>0.000589757461734702</v>
-      </c>
+        <v>0.00103247683843141</v>
+      </c>
+      <c r="D256"/>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B257" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C257" t="n">
-        <v>0.00102125172482302</v>
-      </c>
-      <c r="D257"/>
+        <v>0.000962955144979613</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.000463036744950349</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B258" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C258" t="n">
-        <v>0.000953970461917066</v>
+        <v>0.000957679846961798</v>
       </c>
       <c r="D258" t="n">
-        <v>0.000458874995627441</v>
+        <v>0.000398702717070476</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B259" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="C259" t="n">
-        <v>0.0009468086217003</v>
-      </c>
-      <c r="D259" t="n">
-        <v>0.000394707672662093</v>
-      </c>
+        <v>0.000939878522161256</v>
+      </c>
+      <c r="D259"/>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B260" t="s">
         <v>323</v>
       </c>
       <c r="C260" t="n">
-        <v>0.00093077232730189</v>
+        <v>0.000913524480148853</v>
       </c>
       <c r="D260"/>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B261" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="C261" t="n">
-        <v>0.000905127601308316</v>
-      </c>
-      <c r="D261"/>
+        <v>0.000864879498001598</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.000214351520476141</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B262" t="s">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="C262" t="n">
-        <v>0.000877058525676148</v>
+        <v>0.000863891782628049</v>
       </c>
       <c r="D262" t="n">
-        <v>0.000197550427394053</v>
+        <v>0.0002190499838989</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B263" t="s">
-        <v>325</v>
+        <v>184</v>
       </c>
       <c r="C263" t="n">
-        <v>0.000854683335433706</v>
-      </c>
-      <c r="D263" t="n">
-        <v>0.000216517533152928</v>
-      </c>
+        <v>0.000760765318398934</v>
+      </c>
+      <c r="D263"/>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B264" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="C264" t="n">
-        <v>0.000752504782775876</v>
+        <v>0.000751516710810254</v>
       </c>
       <c r="D264"/>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B265" t="s">
-        <v>326</v>
+        <v>122</v>
       </c>
       <c r="C265" t="n">
-        <v>0.000744608965145591</v>
+        <v>0.000747565849316061</v>
       </c>
       <c r="D265"/>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B266" t="s">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="C266" t="n">
-        <v>0.000739604573689776</v>
-      </c>
-      <c r="D266"/>
+        <v>0.000745702658952322</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.00012122353094463</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B267" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C267" t="n">
-        <v>0.000737625058847254</v>
+        <v>0.00073266032640615</v>
       </c>
       <c r="D267" t="n">
-        <v>0.000120785549111243</v>
+        <v>0.000173557429271781</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B268" t="s">
-        <v>239</v>
+        <v>326</v>
       </c>
       <c r="C268" t="n">
-        <v>0.00072512520107762</v>
-      </c>
-      <c r="D268" t="n">
-        <v>0.000171395952371657</v>
-      </c>
+        <v>0.000706418524777104</v>
+      </c>
+      <c r="D268"/>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B269" t="s">
         <v>327</v>
       </c>
       <c r="C269" t="n">
-        <v>0.000698746497670526</v>
-      </c>
-      <c r="D269"/>
+        <v>0.000699437172932251</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.000175716182736292</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B270" t="s">
-        <v>328</v>
+        <v>224</v>
       </c>
       <c r="C270" t="n">
-        <v>0.000691940525290619</v>
+        <v>0.000658693913773382</v>
       </c>
       <c r="D270" t="n">
-        <v>0.000173346135716683</v>
+        <v>0.000171922490986159</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B271" t="s">
-        <v>224</v>
+        <v>328</v>
       </c>
       <c r="C271" t="n">
-        <v>0.000652461437139193</v>
-      </c>
-      <c r="D271" t="n">
-        <v>0.000170468042554266</v>
-      </c>
+        <v>0.000656381761876212</v>
+      </c>
+      <c r="D271"/>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B272" t="s">
-        <v>329</v>
+        <v>161</v>
       </c>
       <c r="C272" t="n">
-        <v>0.000647701704821219</v>
+        <v>0.00064594340622394</v>
       </c>
       <c r="D272"/>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C273" t="n">
-        <v>0.000639027426297807</v>
-      </c>
-      <c r="D273"/>
+        <v>0.000636335629408515</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.0000141747562044723</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B274" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C274" t="n">
-        <v>0.000628862951207552</v>
-      </c>
-      <c r="D274" t="n">
-        <v>0.0000133052831442854</v>
-      </c>
+        <v>0.000631688877537504</v>
+      </c>
+      <c r="D274"/>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B275" t="s">
-        <v>157</v>
+        <v>329</v>
       </c>
       <c r="C275" t="n">
-        <v>0.00062350269191488</v>
+        <v>0.000574266697411671</v>
       </c>
       <c r="D275"/>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B276" t="s">
-        <v>330</v>
+        <v>126</v>
       </c>
       <c r="C276" t="n">
-        <v>0.000566808497155452</v>
+        <v>0.000568564885937097</v>
       </c>
       <c r="D276"/>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B277" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="C277" t="n">
-        <v>0.000562137731796692</v>
-      </c>
-      <c r="D277"/>
+        <v>0.000568564885937097</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.000123556889468771</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B278" t="s">
-        <v>331</v>
+        <v>218</v>
       </c>
       <c r="C278" t="n">
-        <v>0.000562137731796692</v>
-      </c>
-      <c r="D278" t="n">
-        <v>0.000122704277886187</v>
-      </c>
+        <v>0.000561291709095513</v>
+      </c>
+      <c r="D278"/>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B279" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="C279" t="n">
-        <v>0.000555910044651679</v>
+        <v>0.000502522644369387</v>
       </c>
       <c r="D279"/>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B280" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="C280" t="n">
-        <v>0.000497636686366194</v>
+        <v>0.000495541292524534</v>
       </c>
       <c r="D280"/>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B281" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C281" t="n">
-        <v>0.000490452604409625</v>
-      </c>
-      <c r="D281"/>
+        <v>0.000490782300270165</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.000161382694659429</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B282" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="C282" t="n">
-        <v>0.000485403729474203</v>
-      </c>
-      <c r="D282" t="n">
-        <v>0.000160040852572397</v>
-      </c>
+        <v>0.000444696398863467</v>
+      </c>
+      <c r="D282"/>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B283" t="s">
         <v>332</v>
       </c>
       <c r="C283" t="n">
-        <v>0.000439519020259335</v>
-      </c>
-      <c r="D283"/>
+        <v>0.000408330514655551</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.000103080477930395</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B284" t="s">
         <v>333</v>
       </c>
       <c r="C284" t="n">
-        <v>0.000403776544394918</v>
-      </c>
-      <c r="D284" t="n">
-        <v>0.000102321716473665</v>
-      </c>
+        <v>0.000393829057125727</v>
+      </c>
+      <c r="D284"/>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>334</v>
+        <v>147</v>
       </c>
       <c r="C285" t="n">
-        <v>0.000388607677848849</v>
+        <v>0.000365409792059541</v>
       </c>
       <c r="D285"/>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B286" t="s">
-        <v>148</v>
+        <v>334</v>
       </c>
       <c r="C286" t="n">
-        <v>0.000362051040523327</v>
-      </c>
-      <c r="D286"/>
+        <v>0.000365275103599512</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.000113017093142041</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B287" t="s">
         <v>335</v>
       </c>
       <c r="C287" t="n">
-        <v>0.000360738777874913</v>
-      </c>
-      <c r="D287" t="n">
-        <v>0.000111301996231806</v>
-      </c>
+        <v>0.00034630647881205</v>
+      </c>
+      <c r="D287"/>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B288" t="s">
-        <v>336</v>
+        <v>228</v>
       </c>
       <c r="C288" t="n">
-        <v>0.000342811935593195</v>
+        <v>0.000328190880938106</v>
       </c>
       <c r="D288"/>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B289" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="C289" t="n">
-        <v>0.000323839731540707</v>
+        <v>0.000308144748470409</v>
       </c>
       <c r="D289"/>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B290" t="s">
-        <v>202</v>
+        <v>336</v>
       </c>
       <c r="C290" t="n">
-        <v>0.000305023219666845</v>
+        <v>0.000308144748470409</v>
       </c>
       <c r="D290"/>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B291" t="s">
-        <v>337</v>
+        <v>186</v>
       </c>
       <c r="C291" t="n">
-        <v>0.000305023219666845</v>
+        <v>0.000226860262842716</v>
       </c>
       <c r="D291"/>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B292" t="s">
-        <v>186</v>
+        <v>337</v>
       </c>
       <c r="C292" t="n">
-        <v>0.000224775022455384</v>
+        <v>0.000217364726410649</v>
       </c>
       <c r="D292"/>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B293" t="s">
         <v>338</v>
       </c>
       <c r="C293" t="n">
-        <v>0.000215010898681595</v>
+        <v>0.000207779397671895</v>
       </c>
       <c r="D293"/>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B294" t="s">
         <v>339</v>
       </c>
       <c r="C294" t="n">
-        <v>0.000205691609703878</v>
+        <v>0.000196914528562864</v>
       </c>
       <c r="D294"/>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B295" t="s">
         <v>340</v>
       </c>
       <c r="C295" t="n">
-        <v>0.000194303838924424</v>
+        <v>0.000182704896029771</v>
       </c>
       <c r="D295"/>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B296" t="s">
         <v>341</v>
       </c>
       <c r="C296" t="n">
-        <v>0.000181025520261663</v>
+        <v>0.000182704896029771</v>
       </c>
       <c r="D296"/>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B297" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="C297" t="n">
-        <v>0.000181025520261663</v>
+        <v>0.000154061150196869</v>
       </c>
       <c r="D297"/>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B298" t="s">
-        <v>92</v>
+        <v>256</v>
       </c>
       <c r="C298" t="n">
-        <v>0.000152511609833422</v>
+        <v>0.000154061150196869</v>
       </c>
       <c r="D298"/>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B299" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="C299" t="n">
-        <v>0.000152511609833422</v>
+        <v>0.000131276352375242</v>
       </c>
       <c r="D299"/>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B300" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="C300" t="n">
-        <v>0.000129535892616283</v>
+        <v>0.000102722398849027</v>
       </c>
       <c r="D300"/>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B301" t="s">
-        <v>182</v>
+        <v>342</v>
       </c>
       <c r="C301" t="n">
-        <v>0.000101666992642347</v>
+        <v>0.000102722398849027</v>
       </c>
       <c r="D301"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="s">
-        <v>284</v>
-      </c>
-      <c r="B302" t="s">
-        <v>343</v>
-      </c>
-      <c r="C302" t="n">
-        <v>0.000101666992642347</v>
-      </c>
-      <c r="D302"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
